--- a/franquias/pwr_reports/Keys Summary - Franquias (Stores)(2026-08-24 - 2026-08-30).xlsx
+++ b/franquias/pwr_reports/Keys Summary - Franquias (Stores)(2026-08-24 - 2026-08-30).xlsx
@@ -404,7 +404,7 @@
     <t>Jardim Tavares-Campina Grande</t>
   </si>
   <si>
-    <t>Alcantara de Medeiros Junior,Pedro</t>
+    <t>OLIVEIRA,MARCOS VICTOR SILVA</t>
   </si>
   <si>
     <t>Fazenda Santa Genebra-Campinas</t>
@@ -485,9 +485,6 @@
     <t>Joao Pessoa</t>
   </si>
   <si>
-    <t>OLIVEIRA,MARCOS VICTOR SILVA</t>
-  </si>
-  <si>
     <t>Joinville</t>
   </si>
   <si>
@@ -783,9 +780,6 @@
   </si>
   <si>
     <t>Cachoeiro de Itapemirim</t>
-  </si>
-  <si>
-    <t>DURANTE,DANIEL BARROS and DANIELA PIMENTEL MOREIRA</t>
   </si>
   <si>
     <t>AP</t>
@@ -864,66 +858,66 @@
 153</t>
   </si>
   <si>
-    <t>160</t>
-  </si>
-  <si>
-    <t>R$ 6.298.946,93</t>
-  </si>
-  <si>
-    <t>R$ 41.675,45
-R$ 40.059,65</t>
-  </si>
-  <si>
-    <t>4.1%
-3.4%</t>
-  </si>
-  <si>
-    <t>450.1</t>
-  </si>
-  <si>
-    <t>(9.5%)</t>
-  </si>
-  <si>
-    <t>21.9%</t>
-  </si>
-  <si>
-    <t>(18.8%)</t>
-  </si>
-  <si>
-    <t>3.1%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>28.8</t>
-  </si>
-  <si>
-    <t>65.1%</t>
-  </si>
-  <si>
-    <t>13.3%</t>
+    <t>122</t>
+  </si>
+  <si>
+    <t>R$ 6.578.505,63</t>
+  </si>
+  <si>
+    <t>R$ 42.016,00
+R$ 41.642,38</t>
+  </si>
+  <si>
+    <t>(4.7%)
+(3.5%)</t>
+  </si>
+  <si>
+    <t>454.2</t>
+  </si>
+  <si>
+    <t>(10.0%)</t>
+  </si>
+  <si>
+    <t>24.1%</t>
+  </si>
+  <si>
+    <t>(17.1%)</t>
+  </si>
+  <si>
+    <t>3.2%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>28.9</t>
+  </si>
+  <si>
+    <t>64.6%</t>
+  </si>
+  <si>
+    <t>13.6%</t>
   </si>
   <si>
     <t>5.8</t>
   </si>
   <si>
-    <t>7.7</t>
-  </si>
-  <si>
-    <t>13.2</t>
-  </si>
-  <si>
-    <t>20.2</t>
-  </si>
-  <si>
-    <t>65.5%</t>
-  </si>
-  <si>
-    <t>-R$ 202.288,98</t>
-  </si>
-  <si>
-    <t>2.74</t>
+    <t>7.8</t>
+  </si>
+  <si>
+    <t>13.7</t>
+  </si>
+  <si>
+    <t>20.3</t>
+  </si>
+  <si>
+    <t>65.2%</t>
+  </si>
+  <si>
+    <t>-R$ 218.504,65</t>
+  </si>
+  <si>
+    <t>2.76</t>
   </si>
   <si>
     <t>3.40</t>
@@ -1576,7 +1570,7 @@
         <v>54735.279999999992</v>
       </c>
       <c r="Q2" s="6">
-        <v>0.071007418843255232</v>
+        <v>-0.043610341570980204</v>
       </c>
       <c r="R2" s="7">
         <v>568</v>
@@ -1662,7 +1656,7 @@
         <v>19513</v>
       </c>
       <c r="B3" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C3" s="4">
         <v>44</v>
@@ -1699,55 +1693,55 @@
         <v>52</v>
       </c>
       <c r="O3" s="5">
-        <v>54971.43</v>
+        <v>68470.880000000005</v>
       </c>
       <c r="P3" s="5">
-        <v>64133.334999999999</v>
+        <v>68470.880000000005</v>
       </c>
       <c r="Q3" s="6">
-        <v>0.041289368408764515</v>
+        <v>0.05520726611902016</v>
       </c>
       <c r="R3" s="7">
-        <v>634.66666666666674</v>
+        <v>681</v>
       </c>
       <c r="S3" s="6">
-        <v>0.034220532319391594</v>
+        <v>0.046082949308755783</v>
       </c>
       <c r="T3" s="6">
-        <v>0.71956328405500825</v>
+        <v>0.63617009595904128</v>
       </c>
       <c r="U3" s="6">
-        <v>0.39082233625721574</v>
+        <v>0.30946405683700867</v>
       </c>
       <c r="V3" s="6">
-        <v>0.024436229874318351</v>
+        <v>0.024565099791327347</v>
       </c>
       <c r="W3" s="6">
-        <v>0.0048360484709966609</v>
+        <v>0.0047208974092344076</v>
       </c>
       <c r="X3" s="8">
-        <v>23.126966666666668</v>
+        <v>23.502761341222879</v>
       </c>
       <c r="Y3" s="6">
-        <v>0.46958637469586373</v>
+        <v>0.42209072978303747</v>
       </c>
       <c r="Z3" s="6">
-        <v>0.012165450121654502</v>
+        <v>0.011834319526627219</v>
       </c>
       <c r="AA3" s="8">
-        <v>4.8985854243542439</v>
+        <v>5.3417033873343147</v>
       </c>
       <c r="AB3" s="8">
-        <v>4.5497933002481394</v>
+        <v>4.6258737903225802</v>
       </c>
       <c r="AC3" s="8">
-        <v>9.6491299999999995</v>
+        <v>10.301685000000001</v>
       </c>
       <c r="AD3" s="8">
-        <v>15.323681995133819</v>
+        <v>15.947501577909271</v>
       </c>
       <c r="AE3" s="6">
-        <v>0.84184914841849146</v>
+        <v>0.81459566074950696</v>
       </c>
       <c r="AF3" s="9"/>
       <c r="AG3" s="5">
@@ -1836,7 +1830,7 @@
         <v>62966.659999999996</v>
       </c>
       <c r="Q4" s="6">
-        <v>0.09168281507867837</v>
+        <v>0.038789983863833921</v>
       </c>
       <c r="R4" s="7">
         <v>700</v>
@@ -1967,7 +1961,7 @@
         <v>23273.889999999996</v>
       </c>
       <c r="Q5" s="6">
-        <v>0.0075695786491558614</v>
+        <v>-0.087466981588890769</v>
       </c>
       <c r="R5" s="7">
         <v>241</v>
@@ -2055,7 +2049,7 @@
         <v>19521</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2095,22 +2089,22 @@
         <v>76227.809999999998</v>
       </c>
       <c r="P6" s="5">
-        <v>88932.444999999992</v>
+        <v>76227.809999999983</v>
       </c>
       <c r="Q6" s="6">
-        <v>0.39403100579558004</v>
+        <v>0.056841927508792578</v>
       </c>
       <c r="R6" s="7">
-        <v>977.66666666666663</v>
+        <v>838</v>
       </c>
       <c r="S6" s="6">
-        <v>0.1370420624151969</v>
+        <v>0.13704206241519667</v>
       </c>
       <c r="T6" s="6">
-        <v>-0.0044633054524326494</v>
+        <v>-0.0019707768070471921</v>
       </c>
       <c r="U6" s="6">
-        <v>-0.36199463161804074</v>
+        <v>-0.35950210297265528</v>
       </c>
       <c r="V6" s="6">
         <v>0.038454371180281846</v>
@@ -2229,7 +2223,7 @@
         <v>71836.630000000005</v>
       </c>
       <c r="Q7" s="6">
-        <v>0.32648890315235013</v>
+        <v>0.1759655352596674</v>
       </c>
       <c r="R7" s="7">
         <v>748</v>
@@ -2265,7 +2259,7 @@
         <v>6.2512233027522939</v>
       </c>
       <c r="AC7" s="8">
-        <v>10.395051</v>
+        <v>10.834769</v>
       </c>
       <c r="AD7" s="8">
         <v>17.740310786106033</v>
@@ -2360,7 +2354,7 @@
         <v>39112.110000000001</v>
       </c>
       <c r="Q8" s="6">
-        <v>-0.0088330988804801169</v>
+        <v>-0.1109206964040943</v>
       </c>
       <c r="R8" s="7">
         <v>463</v>
@@ -2491,7 +2485,7 @@
         <v>98313.199999999997</v>
       </c>
       <c r="Q9" s="6">
-        <v>0.22009765924107949</v>
+        <v>0.16099518529203616</v>
       </c>
       <c r="R9" s="7">
         <v>939</v>
@@ -2622,7 +2616,7 @@
         <v>54890.489999999998</v>
       </c>
       <c r="Q10" s="6">
-        <v>0.061339007679122259</v>
+        <v>-0.055760386500022907</v>
       </c>
       <c r="R10" s="7">
         <v>548</v>
@@ -2753,7 +2747,7 @@
         <v>122137.24000000001</v>
       </c>
       <c r="Q11" s="6">
-        <v>0.30340965541675868</v>
+        <v>0.24104608303125308</v>
       </c>
       <c r="R11" s="7">
         <v>1300</v>
@@ -2789,7 +2783,7 @@
         <v>8.3559887005649713</v>
       </c>
       <c r="AC11" s="8">
-        <v>21.964967999999999</v>
+        <v>21.791149999999998</v>
       </c>
       <c r="AD11" s="8">
         <v>28.568559799554563</v>
@@ -2884,7 +2878,7 @@
         <v>29530.759999999998</v>
       </c>
       <c r="Q12" s="6">
-        <v>-0.30895219677577046</v>
+        <v>0.016805845008299292</v>
       </c>
       <c r="R12" s="7">
         <v>319.66666666666663</v>
@@ -3013,7 +3007,7 @@
         <v>73112.339999999997</v>
       </c>
       <c r="Q13" s="6">
-        <v>0.6810437174640156</v>
+        <v>0.49823531111414865</v>
       </c>
       <c r="R13" s="7">
         <v>703</v>
@@ -3144,7 +3138,7 @@
         <v>112730.84999999999</v>
       </c>
       <c r="Q14" s="6">
-        <v>0.12052127851179817</v>
+        <v>-0.0075802933501161185</v>
       </c>
       <c r="R14" s="7">
         <v>1027</v>
@@ -3275,7 +3269,7 @@
         <v>41854.869999999995</v>
       </c>
       <c r="Q15" s="6">
-        <v>-0.31538823275400285</v>
+        <v>-0.39429499509993193</v>
       </c>
       <c r="R15" s="7">
         <v>403</v>
@@ -3311,7 +3305,7 @@
         <v>8.7687320512820506</v>
       </c>
       <c r="AC15" s="8">
-        <v>13.594108</v>
+        <v>13.806232</v>
       </c>
       <c r="AD15" s="8">
         <v>21.345454545454547</v>
@@ -3363,7 +3357,7 @@
         <v>19546</v>
       </c>
       <c r="B16" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C16" s="4">
         <v>44</v>
@@ -3400,59 +3394,59 @@
         <v>52</v>
       </c>
       <c r="O16" s="5">
-        <v>36027.479999999996</v>
+        <v>42392.419999999998</v>
       </c>
       <c r="P16" s="5">
-        <v>42032.059999999998</v>
+        <v>42392.419999999998</v>
       </c>
       <c r="Q16" s="6">
-        <v>-0.051854669054170577</v>
+        <v>-0.13969629502004111</v>
       </c>
       <c r="R16" s="7">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="S16" s="6">
-        <v>-0.13525498891352561</v>
+        <v>-0.17179023508137437</v>
       </c>
       <c r="T16" s="6">
-        <v>0.00070748495315242697</v>
+        <v>0.00085784439765410904</v>
       </c>
       <c r="U16" s="6">
-        <v>-0.3273645866988199</v>
+        <v>-0.32442035392176244</v>
       </c>
       <c r="V16" s="6">
-        <v>0.065187157136718965</v>
+        <v>0.067977824809246551</v>
       </c>
       <c r="W16" s="6">
-        <v>0.055991398787814187</v>
+        <v>0.05876438523679469</v>
       </c>
       <c r="X16" s="8">
-        <v>24.415342990654203</v>
+        <v>23.99583346153846</v>
       </c>
       <c r="Y16" s="6">
-        <v>0.70560747663551404</v>
+        <v>0.69230769230769229</v>
       </c>
       <c r="Z16" s="6">
-        <v>0.014018691588785047</v>
+        <v>0.011538461538461539</v>
       </c>
       <c r="AA16" s="8">
-        <v>3.49280205655527</v>
+        <v>3.2640043763676152</v>
       </c>
       <c r="AB16" s="8">
-        <v>6.6011682242990659</v>
+        <v>6.3543588461538461</v>
       </c>
       <c r="AC16" s="8">
-        <v>10.028067</v>
+        <v>9.5068479999999997</v>
       </c>
       <c r="AD16" s="8">
-        <v>16.990420560747662</v>
+        <v>16.462756538461541</v>
       </c>
       <c r="AE16" s="6">
-        <v>0.81775700934579443</v>
+        <v>0.82692307692307687</v>
       </c>
       <c r="AF16" s="9"/>
       <c r="AG16" s="5">
-        <v>-8063.7799999999997</v>
+        <v>-9902.3600000000006</v>
       </c>
       <c r="AH16" s="10">
         <v>2</v>
@@ -3537,7 +3531,7 @@
         <v>28665.150000000001</v>
       </c>
       <c r="Q17" s="6">
-        <v>-0.31109452843928209</v>
+        <v>-0.38034333533723608</v>
       </c>
       <c r="R17" s="7">
         <v>342</v>
@@ -3573,7 +3567,7 @@
         <v>9.8424238636363626</v>
       </c>
       <c r="AC17" s="8">
-        <v>17.438921000000001</v>
+        <v>17.575849000000002</v>
       </c>
       <c r="AD17" s="8">
         <v>24.993956043956043</v>
@@ -3700,7 +3694,7 @@
         <v>5.4978764705882357</v>
       </c>
       <c r="AC18" s="8">
-        <v>6.5134350000000003</v>
+        <v>8.6837970000000002</v>
       </c>
       <c r="AD18" s="8">
         <v>15.644281372549019</v>
@@ -3754,7 +3748,7 @@
         <v>19551</v>
       </c>
       <c r="B19" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C19" s="4">
         <v>44</v>
@@ -3791,55 +3785,55 @@
         <v>52</v>
       </c>
       <c r="O19" s="5">
-        <v>47843.199999999997</v>
+        <v>60390.349999999999</v>
       </c>
       <c r="P19" s="5">
-        <v>55817.066666666658</v>
+        <v>60390.349999999999</v>
       </c>
       <c r="Q19" s="6">
-        <v>-0.0010874318729510168</v>
+        <v>-0.067522181926773062</v>
       </c>
       <c r="R19" s="7">
-        <v>542.5</v>
+        <v>587</v>
       </c>
       <c r="S19" s="6">
-        <v>-0.043209876543209846</v>
+        <v>-0.079937304075235138</v>
       </c>
       <c r="T19" s="6">
-        <v>0.34810068515483916</v>
+        <v>0.30322467910849993</v>
       </c>
       <c r="U19" s="6">
-        <v>0.00340196098923149</v>
+        <v>-0.038546812528822902</v>
       </c>
       <c r="V19" s="6">
-        <v>0.020101351916259783</v>
+        <v>0.018614522022144267</v>
       </c>
       <c r="W19" s="6">
-        <v>0.0093136119657548002</v>
+        <v>0.008393518169707577</v>
       </c>
       <c r="X19" s="8">
-        <v>21.336432631578948</v>
+        <v>21.731278991596639</v>
       </c>
       <c r="Y19" s="6">
-        <v>0.90175438596491231</v>
+        <v>0.87114845938375352</v>
       </c>
       <c r="Z19" s="6">
         <v>0</v>
       </c>
       <c r="AA19" s="8">
-        <v>3.4596638655462182</v>
+        <v>3.5595238655462187</v>
       </c>
       <c r="AB19" s="8">
-        <v>4.4204442446043162</v>
+        <v>4.6172896551724136</v>
       </c>
       <c r="AC19" s="8">
         <v>8.0970279999999999</v>
       </c>
       <c r="AD19" s="8">
-        <v>15.82953192982456</v>
+        <v>16.0913162464986</v>
       </c>
       <c r="AE19" s="6">
-        <v>0.9508771929824561</v>
+        <v>0.9327731092436975</v>
       </c>
       <c r="AF19" s="9"/>
       <c r="AG19" s="5">
@@ -3928,7 +3922,7 @@
         <v>88497.640000000014</v>
       </c>
       <c r="Q20" s="6">
-        <v>0.098750370915736907</v>
+        <v>-0.073643146728685105</v>
       </c>
       <c r="R20" s="7">
         <v>870</v>
@@ -3964,7 +3958,7 @@
         <v>4.720594108761329</v>
       </c>
       <c r="AC20" s="8">
-        <v>7.5721740000000004</v>
+        <v>7.5682130000000001</v>
       </c>
       <c r="AD20" s="8">
         <v>13.536580966767371</v>
@@ -4016,7 +4010,7 @@
         <v>19553</v>
       </c>
       <c r="B21" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C21" s="4">
         <v>44</v>
@@ -4051,55 +4045,55 @@
         <v>52</v>
       </c>
       <c r="O21" s="5">
-        <v>44817.07</v>
+        <v>55975.479999999996</v>
       </c>
       <c r="P21" s="5">
-        <v>52286.581666666665</v>
+        <v>55975.479999999996</v>
       </c>
       <c r="Q21" s="6">
-        <v>0.20452570206776977</v>
+        <v>0.14904063371074638</v>
       </c>
       <c r="R21" s="7">
-        <v>477.16666666666669</v>
+        <v>512</v>
       </c>
       <c r="S21" s="6">
-        <v>0.18550724637681171</v>
+        <v>0.049180327868852514</v>
       </c>
       <c r="T21" s="6">
-        <v>0.30922914416315034</v>
+        <v>0.30809040315509573</v>
       </c>
       <c r="U21" s="6">
-        <v>-0.03161219151542035</v>
+        <v>-0.03645867440529317</v>
       </c>
       <c r="V21" s="6">
-        <v>0.026705906923411103</v>
+        <v>0.026973819608156997</v>
       </c>
       <c r="W21" s="6">
-        <v>-0.0010529358568063464</v>
+        <v>0.0008977591616900828</v>
       </c>
       <c r="X21" s="8">
-        <v>28.965293725490199</v>
+        <v>29.962820307692308</v>
       </c>
       <c r="Y21" s="6">
-        <v>0.8666666666666667</v>
+        <v>0.81538461538461537</v>
       </c>
       <c r="Z21" s="6">
-        <v>0.086274509803921567</v>
+        <v>0.11076923076923077</v>
       </c>
       <c r="AA21" s="8">
-        <v>3.344417831325301</v>
+        <v>3.5740318095238095</v>
       </c>
       <c r="AB21" s="8">
-        <v>9.7780185039370089</v>
+        <v>10.820072445820434</v>
       </c>
       <c r="AC21" s="8">
-        <v>12.983096</v>
+        <v>14.290521</v>
       </c>
       <c r="AD21" s="8">
-        <v>19.878365882352941</v>
+        <v>21.14723076923077</v>
       </c>
       <c r="AE21" s="6">
-        <v>0.62352941176470589</v>
+        <v>0.57846153846153847</v>
       </c>
       <c r="AF21" s="9"/>
       <c r="AG21" s="5">
@@ -4188,7 +4182,7 @@
         <v>55104.709999999999</v>
       </c>
       <c r="Q22" s="6">
-        <v>-0.0073301769971765296</v>
+        <v>-0.11537736044424485</v>
       </c>
       <c r="R22" s="7">
         <v>579</v>
@@ -4319,7 +4313,7 @@
         <v>29730.920000000002</v>
       </c>
       <c r="Q23" s="6">
-        <v>0.1271386728153785</v>
+        <v>0.023335315919617239</v>
       </c>
       <c r="R23" s="7">
         <v>334</v>
@@ -4407,7 +4401,7 @@
         <v>19565</v>
       </c>
       <c r="B24" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C24" s="4">
         <v>44</v>
@@ -4444,55 +4438,55 @@
         <v>52</v>
       </c>
       <c r="O24" s="5">
-        <v>39511.490000000005</v>
+        <v>53148.700000000004</v>
       </c>
       <c r="P24" s="5">
-        <v>46096.738333333342</v>
+        <v>53148.700000000004</v>
       </c>
       <c r="Q24" s="6">
-        <v>-0.13276781153178074</v>
+        <v>-0.11035604371765451</v>
       </c>
       <c r="R24" s="7">
-        <v>518</v>
+        <v>590</v>
       </c>
       <c r="S24" s="6">
-        <v>-0.1445086705202312</v>
+        <v>-0.17018284106891701</v>
       </c>
       <c r="T24" s="6">
-        <v>0.31967675984884397</v>
+        <v>0.28012953280136677</v>
       </c>
       <c r="U24" s="6">
-        <v>0.0010499502802855576</v>
+        <v>-0.034964157166591098</v>
       </c>
       <c r="V24" s="6">
-        <v>0.076409874697208335</v>
+        <v>0.070082165697373591</v>
       </c>
       <c r="W24" s="6">
-        <v>0.042794083442563163</v>
+        <v>0.03965903211179201</v>
       </c>
       <c r="X24" s="8">
-        <v>28.596255056179775</v>
+        <v>27.846784782608694</v>
       </c>
       <c r="Y24" s="6">
-        <v>0.88014981273408244</v>
+        <v>0.875</v>
       </c>
       <c r="Z24" s="6">
-        <v>0.10486891385767791</v>
+        <v>0.084239130434782608</v>
       </c>
       <c r="AA24" s="8">
-        <v>3.1253382882882885</v>
+        <v>3.0908887945670629</v>
       </c>
       <c r="AB24" s="8">
-        <v>8.6664081395348838</v>
+        <v>8.2006571830985919</v>
       </c>
       <c r="AC24" s="8">
-        <v>11.856593</v>
+        <v>11.325139999999999</v>
       </c>
       <c r="AD24" s="8">
-        <v>19.387016479400749</v>
+        <v>18.824275543478262</v>
       </c>
       <c r="AE24" s="6">
-        <v>0.62546816479400746</v>
+        <v>0.66304347826086951</v>
       </c>
       <c r="AF24" s="9"/>
       <c r="AG24" s="5">
@@ -4581,7 +4575,7 @@
         <v>95861.990000000005</v>
       </c>
       <c r="Q25" s="6">
-        <v>0.16607445764857087</v>
+        <v>-0.0090505731385296384</v>
       </c>
       <c r="R25" s="7">
         <v>1164</v>
@@ -4617,7 +4611,7 @@
         <v>7.2764141898370092</v>
       </c>
       <c r="AC25" s="8">
-        <v>10.07155</v>
+        <v>10.942326</v>
       </c>
       <c r="AD25" s="8">
         <v>17.440154351851852</v>
@@ -4712,7 +4706,7 @@
         <v>40408.449999999997</v>
       </c>
       <c r="Q26" s="6">
-        <v>-0.033943566847764339</v>
+        <v>-0.17463299274319144</v>
       </c>
       <c r="R26" s="7">
         <v>489</v>
@@ -4843,7 +4837,7 @@
         <v>31031.385000000002</v>
       </c>
       <c r="Q27" s="6">
-        <v>-0.31219096521255729</v>
+        <v>-0.20952252311288766</v>
       </c>
       <c r="R27" s="7">
         <v>264.25</v>
@@ -4931,7 +4925,7 @@
         <v>19580</v>
       </c>
       <c r="B28" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C28" s="4">
         <v>44</v>
@@ -4968,55 +4962,55 @@
         <v>52</v>
       </c>
       <c r="O28" s="5">
-        <v>38212.510000000002</v>
+        <v>45684.410000000003</v>
       </c>
       <c r="P28" s="5">
-        <v>44581.261666666665</v>
+        <v>45684.409999999996</v>
       </c>
       <c r="Q28" s="6">
-        <v>-0.14066529924902538</v>
+        <v>-0.16272625789244</v>
       </c>
       <c r="R28" s="7">
-        <v>446.83333333333337</v>
+        <v>466</v>
       </c>
       <c r="S28" s="6">
-        <v>-0.10304449648711944</v>
+        <v>-0.16036036036036039</v>
       </c>
       <c r="T28" s="6">
-        <v>0.29626882138859761</v>
+        <v>0.30498429332894961</v>
       </c>
       <c r="U28" s="6">
-        <v>-0.033704268575919245</v>
+        <v>-0.026472980607607711</v>
       </c>
       <c r="V28" s="6">
-        <v>0.024224409754815896</v>
+        <v>0.02390121706726649</v>
       </c>
       <c r="W28" s="6">
-        <v>0.0023682165866623262</v>
+        <v>0.0023846865922094646</v>
       </c>
       <c r="X28" s="8">
-        <v>33.600976556776558</v>
+        <v>37.206993750000002</v>
       </c>
       <c r="Y28" s="6">
-        <v>0.69230769230769229</v>
+        <v>0.6607142857142857</v>
       </c>
       <c r="Z28" s="6">
-        <v>0.21611721611721613</v>
+        <v>0.30654761904761907</v>
       </c>
       <c r="AA28" s="8">
-        <v>6.3780188775510203</v>
+        <v>8.3423670168067225</v>
       </c>
       <c r="AB28" s="8">
-        <v>8.3299490421455946</v>
+        <v>9.3327124223602489</v>
       </c>
       <c r="AC28" s="8">
-        <v>14.995822</v>
+        <v>18.021391000000001</v>
       </c>
       <c r="AD28" s="8">
-        <v>21.448657142857144</v>
+        <v>24.475198511904761</v>
       </c>
       <c r="AE28" s="6">
-        <v>0.304029304029304</v>
+        <v>0.26190476190476192</v>
       </c>
       <c r="AF28" s="9"/>
       <c r="AG28" s="5">
@@ -5062,7 +5056,7 @@
         <v>19581</v>
       </c>
       <c r="B29" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C29" s="4">
         <v>44</v>
@@ -5099,55 +5093,55 @@
         <v>52</v>
       </c>
       <c r="O29" s="5">
-        <v>38844.639999999999</v>
+        <v>53114.82</v>
       </c>
       <c r="P29" s="5">
-        <v>45318.746666666666</v>
+        <v>53114.82</v>
       </c>
       <c r="Q29" s="6">
-        <v>-0.15274151102472944</v>
+        <v>-0.055846642595992368</v>
       </c>
       <c r="R29" s="7">
-        <v>457.33333333333331</v>
+        <v>541</v>
       </c>
       <c r="S29" s="6">
-        <v>-0.19341563786008231</v>
+        <v>-0.13022508038585212</v>
       </c>
       <c r="T29" s="6">
-        <v>0.32456358200256202</v>
+        <v>0.31619101599139371</v>
       </c>
       <c r="U29" s="6">
-        <v>0.0016503049069318189</v>
+        <v>-0.0057328839672242133</v>
       </c>
       <c r="V29" s="6">
-        <v>0.041177946300956836</v>
+        <v>0.0353089213142396</v>
       </c>
       <c r="W29" s="6">
-        <v>0.017195486944916981</v>
+        <v>0.013922799700723828</v>
       </c>
       <c r="X29" s="8">
-        <v>46.012950819672135</v>
+        <v>51.936538461538461</v>
       </c>
       <c r="Y29" s="6">
-        <v>0.24836601307189543</v>
+        <v>0.18854415274463007</v>
       </c>
       <c r="Z29" s="6">
-        <v>0.56721311475409841</v>
+        <v>0.65625</v>
       </c>
       <c r="AA29" s="8">
-        <v>5.0800002564102567</v>
+        <v>6.0313113970588228</v>
       </c>
       <c r="AB29" s="8">
-        <v>20.275675675675679</v>
+        <v>24.714567901234567</v>
       </c>
       <c r="AC29" s="8">
-        <v>22.84948</v>
+        <v>30.725431</v>
       </c>
       <c r="AD29" s="8">
-        <v>32.673958552631582</v>
+        <v>37.952369638554217</v>
       </c>
       <c r="AE29" s="6">
-        <v>0.17377049180327869</v>
+        <v>0.13221153846153846</v>
       </c>
       <c r="AF29" s="9"/>
       <c r="AG29" s="5">
@@ -5236,7 +5230,7 @@
         <v>79604.199999999997</v>
       </c>
       <c r="Q30" s="6">
-        <v>0.30744531110136597</v>
+        <v>0.15366182072142665</v>
       </c>
       <c r="R30" s="7">
         <v>829</v>
@@ -5272,7 +5266,7 @@
         <v>4.5740217391304352</v>
       </c>
       <c r="AC30" s="8">
-        <v>10.423295</v>
+        <v>15.841208</v>
       </c>
       <c r="AD30" s="8">
         <v>22.512795698924734</v>
@@ -5324,7 +5318,7 @@
         <v>19596</v>
       </c>
       <c r="B31" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C31" s="4">
         <v>44</v>
@@ -5359,59 +5353,57 @@
         <v>52</v>
       </c>
       <c r="O31" s="5">
-        <v>37570.089999999997</v>
+        <v>46345.25</v>
       </c>
       <c r="P31" s="5">
-        <v>43831.771666666667</v>
-      </c>
-      <c r="Q31" s="6">
-        <v>-0.043905044682126748</v>
-      </c>
+        <v>46345.25</v>
+      </c>
+      <c r="Q31" s="6"/>
       <c r="R31" s="7">
-        <v>476</v>
+        <v>512</v>
       </c>
       <c r="S31" s="6">
-        <v>-0.070615034168565072</v>
+        <v>-0.082437275985663083</v>
       </c>
       <c r="T31" s="6">
-        <v>0.35287301680672045</v>
+        <v>0.3560519125476721</v>
       </c>
       <c r="U31" s="6">
-        <v>0.013229699476365375</v>
+        <v>0.013205774054514756</v>
       </c>
       <c r="V31" s="6">
-        <v>0.049322093718700173</v>
+        <v>0.071828202458720153</v>
       </c>
       <c r="W31" s="6">
-        <v>-0.040576812565527531</v>
+        <v>-0.016265615138552493</v>
       </c>
       <c r="X31" s="8">
-        <v>28.189151724137933</v>
+        <v>27.582930689655171</v>
       </c>
       <c r="Y31" s="6">
-        <v>0.84913793103448276</v>
+        <v>0.8655172413793103</v>
       </c>
       <c r="Z31" s="6">
-        <v>0.090517241379310345</v>
+        <v>0.07586206896551724</v>
       </c>
       <c r="AA31" s="8">
-        <v>4.2604164999999998</v>
+        <v>3.9063364356435644</v>
       </c>
       <c r="AB31" s="8">
-        <v>8.4050209606986908</v>
+        <v>8.2962695804195796</v>
       </c>
       <c r="AC31" s="8">
-        <v>13.196723</v>
+        <v>12.648942999999999</v>
       </c>
       <c r="AD31" s="8">
-        <v>19.969324999999998</v>
+        <v>19.410919655172414</v>
       </c>
       <c r="AE31" s="6">
-        <v>0.63793103448275867</v>
+        <v>0.66551724137931034</v>
       </c>
       <c r="AF31" s="9"/>
       <c r="AG31" s="5">
-        <v>1644.25</v>
+        <v>1999.6500000000001</v>
       </c>
       <c r="AH31" s="10">
         <v>3</v>
@@ -5496,7 +5488,7 @@
         <v>62354.379999999997</v>
       </c>
       <c r="Q32" s="6">
-        <v>-0.012019088320081583</v>
+        <v>-0.12412244568290132</v>
       </c>
       <c r="R32" s="7">
         <v>714</v>
@@ -5625,7 +5617,7 @@
         <v>51766.849999999999</v>
       </c>
       <c r="Q33" s="6">
-        <v>0.13671691698870481</v>
+        <v>0.12607132291521639</v>
       </c>
       <c r="R33" s="7">
         <v>597</v>
@@ -5754,7 +5746,7 @@
         <v>44203.450000000004</v>
       </c>
       <c r="Q34" s="6">
-        <v>0.038458249483983131</v>
+        <v>-0.010556670644276345</v>
       </c>
       <c r="R34" s="7">
         <v>515</v>
@@ -5790,7 +5782,7 @@
         <v>7.1952020202020206</v>
       </c>
       <c r="AC34" s="8">
-        <v>12.650732</v>
+        <v>12.167933</v>
       </c>
       <c r="AD34" s="8">
         <v>19.749795331695331</v>
@@ -5842,7 +5834,7 @@
         <v>19601</v>
       </c>
       <c r="B35" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C35" s="4">
         <v>44</v>
@@ -5879,55 +5871,55 @@
         <v>52</v>
       </c>
       <c r="O35" s="5">
-        <v>31610.189999999995</v>
+        <v>44406.529999999999</v>
       </c>
       <c r="P35" s="5">
-        <v>36878.554999999993</v>
+        <v>44406.529999999992</v>
       </c>
       <c r="Q35" s="6">
-        <v>-0.30725412991710599</v>
+        <v>-0.26011498188464655</v>
       </c>
       <c r="R35" s="7">
-        <v>434</v>
+        <v>522</v>
       </c>
       <c r="S35" s="6">
-        <v>-0.27343749999999989</v>
+        <v>-0.25641025641025639</v>
       </c>
       <c r="T35" s="6">
-        <v>0.20652442772409782</v>
+        <v>0.19532872755425834</v>
       </c>
       <c r="U35" s="6">
-        <v>-0.104060861386787</v>
+        <v>-0.11193419075978241</v>
       </c>
       <c r="V35" s="6">
-        <v>0.074356591972398772</v>
+        <v>0.070479431741232654</v>
       </c>
       <c r="W35" s="6">
-        <v>0.032352099117404859</v>
+        <v>0.034296464956843062</v>
       </c>
       <c r="X35" s="8">
-        <v>23.250071186440678</v>
+        <v>24.587438575667655</v>
       </c>
       <c r="Y35" s="6">
-        <v>0.94117647058823528</v>
+        <v>0.91740412979351027</v>
       </c>
       <c r="Z35" s="6">
-        <v>0.029661016949152543</v>
+        <v>0.044510385756676561</v>
       </c>
       <c r="AA35" s="8">
-        <v>3.0842489010989009</v>
+        <v>3.2424330724070449</v>
       </c>
       <c r="AB35" s="8">
-        <v>5.6557031111111113</v>
+        <v>6.7802653374233133</v>
       </c>
       <c r="AC35" s="8">
-        <v>8.812576</v>
+        <v>10.096591999999999</v>
       </c>
       <c r="AD35" s="8">
-        <v>16.326200423728814</v>
+        <v>17.700593471810091</v>
       </c>
       <c r="AE35" s="6">
-        <v>0.85169491525423724</v>
+        <v>0.79228486646884277</v>
       </c>
       <c r="AF35" s="9"/>
       <c r="AG35" s="5">
@@ -6111,7 +6103,7 @@
         <v>38490.389999999999</v>
       </c>
       <c r="Q37" s="6">
-        <v>-0.082064815726796247</v>
+        <v>-0.17734870016427218</v>
       </c>
       <c r="R37" s="7">
         <v>401</v>
@@ -6240,7 +6232,7 @@
         <v>35355.419999999998</v>
       </c>
       <c r="Q38" s="6">
-        <v>0.25074537949615605</v>
+        <v>0.18295520816987243</v>
       </c>
       <c r="R38" s="7">
         <v>431</v>
@@ -6276,7 +6268,7 @@
         <v>3.8344402343750001</v>
       </c>
       <c r="AC38" s="8">
-        <v>5.8897899999999996</v>
+        <v>6.6624990000000004</v>
       </c>
       <c r="AD38" s="8">
         <v>13.588346874999999</v>
@@ -6289,7 +6281,7 @@
         <v>-83.799999999999997</v>
       </c>
       <c r="AH38" s="10">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AI38" s="11"/>
       <c r="AJ38" s="12">
@@ -6371,7 +6363,7 @@
         <v>38481.120000000003</v>
       </c>
       <c r="Q39" s="6">
-        <v>0.14387936823312342</v>
+        <v>0.032274540553286268</v>
       </c>
       <c r="R39" s="7">
         <v>420</v>
@@ -6407,7 +6399,7 @@
         <v>9.8849609427609426</v>
       </c>
       <c r="AC39" s="8">
-        <v>14.817777</v>
+        <v>16.197375999999998</v>
       </c>
       <c r="AD39" s="8">
         <v>23.00958795986622</v>
@@ -6459,7 +6451,7 @@
         <v>19615</v>
       </c>
       <c r="B40" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C40" s="4">
         <v>44</v>
@@ -6496,55 +6488,55 @@
         <v>52</v>
       </c>
       <c r="O40" s="5">
-        <v>33441.989999999998</v>
+        <v>41905.129999999997</v>
       </c>
       <c r="P40" s="5">
-        <v>39015.654999999999</v>
+        <v>41905.129999999997</v>
       </c>
       <c r="Q40" s="6">
-        <v>-0.060743241388906744</v>
+        <v>-0.098341474162469411</v>
       </c>
       <c r="R40" s="7">
-        <v>467.83333333333331</v>
+        <v>508.99999999999994</v>
       </c>
       <c r="S40" s="6">
-        <v>-0.067441860465116354</v>
+        <v>-0.07285974499089265</v>
       </c>
       <c r="T40" s="6">
-        <v>-2.6912274060245816E-06</v>
+        <v>2.0761181268259998E-05</v>
       </c>
       <c r="U40" s="6">
-        <v>-0.34425582927331777</v>
+        <v>-0.34220702811326442</v>
       </c>
       <c r="V40" s="6">
-        <v>0.091955383037911315</v>
+        <v>0.092989545671377238</v>
       </c>
       <c r="W40" s="6">
-        <v>0.057624591120325079</v>
+        <v>0.057847070275166793</v>
       </c>
       <c r="X40" s="8">
-        <v>31.358115686274509</v>
+        <v>31.000879648241206</v>
       </c>
       <c r="Y40" s="6">
-        <v>0.13915857605177995</v>
+        <v>0.12718204488778054</v>
       </c>
       <c r="Z40" s="6">
-        <v>0.19281045751633988</v>
+        <v>0.16834170854271358</v>
       </c>
       <c r="AA40" s="8">
-        <v>3.5638628504672898</v>
+        <v>3.5886334558823529</v>
       </c>
       <c r="AB40" s="8">
-        <v>9.8927152317880793</v>
+        <v>8.9503383248730977</v>
       </c>
       <c r="AC40" s="8">
-        <v>13.366742</v>
+        <v>12.493776</v>
       </c>
       <c r="AD40" s="8">
-        <v>20.086928104575165</v>
+        <v>19.266122361809046</v>
       </c>
       <c r="AE40" s="6">
-        <v>0.51960784313725494</v>
+        <v>0.52261306532663321</v>
       </c>
       <c r="AF40" s="9"/>
       <c r="AG40" s="5">
@@ -6631,7 +6623,7 @@
         <v>64453.280000000006</v>
       </c>
       <c r="Q41" s="6">
-        <v>-0.014356629372145546</v>
+        <v>-0.12898689506184324</v>
       </c>
       <c r="R41" s="7">
         <v>794</v>
@@ -6667,7 +6659,7 @@
         <v>8.2129731843575424</v>
       </c>
       <c r="AC41" s="8">
-        <v>12.272176</v>
+        <v>12.462286000000001</v>
       </c>
       <c r="AD41" s="8">
         <v>20.229011367673181</v>
@@ -6762,7 +6754,7 @@
         <v>67286.660000000003</v>
       </c>
       <c r="Q42" s="6">
-        <v>0.12107680698677625</v>
+        <v>-0.011711992498684709</v>
       </c>
       <c r="R42" s="7">
         <v>683</v>
@@ -6798,7 +6790,7 @@
         <v>8.4026650406504064</v>
       </c>
       <c r="AC42" s="8">
-        <v>14.468628000000001</v>
+        <v>29.347591000000001</v>
       </c>
       <c r="AD42" s="8">
         <v>33.716400797872339</v>
@@ -6893,7 +6885,7 @@
         <v>29885.216666666671</v>
       </c>
       <c r="Q43" s="6">
-        <v>-0.34984393611946629</v>
+        <v>-0.001371482214394204</v>
       </c>
       <c r="R43" s="7">
         <v>326.66666666666663</v>
@@ -7024,7 +7016,7 @@
         <v>40793.169999999998</v>
       </c>
       <c r="Q44" s="6">
-        <v>0.085412881165439103</v>
+        <v>-0.018230044110030597</v>
       </c>
       <c r="R44" s="7">
         <v>473.99999999999994</v>
@@ -7155,7 +7147,7 @@
         <v>29059.129999999997</v>
       </c>
       <c r="Q45" s="6">
-        <v>-0.19147529014969844</v>
+        <v>-0.26643551709513902</v>
       </c>
       <c r="R45" s="7">
         <v>332</v>
@@ -7191,7 +7183,7 @@
         <v>3.9560695652173909</v>
       </c>
       <c r="AC45" s="8">
-        <v>8.1896599999999999</v>
+        <v>7.9134359999999999</v>
       </c>
       <c r="AD45" s="8">
         <v>15.670282010582012</v>
@@ -7284,7 +7276,7 @@
         <v>26691.079999999998</v>
       </c>
       <c r="Q46" s="6">
-        <v>-0.066264221490376474</v>
+        <v>-0.15251884450032693</v>
       </c>
       <c r="R46" s="7">
         <v>333</v>
@@ -7320,7 +7312,7 @@
         <v>6.0885254098360662</v>
       </c>
       <c r="AC46" s="8">
-        <v>9.3184889999999996</v>
+        <v>8.5893940000000004</v>
       </c>
       <c r="AD46" s="8">
         <v>14.789141666666666</v>
@@ -7413,7 +7405,7 @@
         <v>49159.169999999998</v>
       </c>
       <c r="Q47" s="6">
-        <v>-0.16029842363693947</v>
+        <v>-0.20883706580459138</v>
       </c>
       <c r="R47" s="7">
         <v>472</v>
@@ -7544,7 +7536,7 @@
         <v>51362.099999999999</v>
       </c>
       <c r="Q48" s="6">
-        <v>0.26340529890268294</v>
+        <v>0.13160644090396145</v>
       </c>
       <c r="R48" s="7">
         <v>555</v>
@@ -7673,7 +7665,7 @@
         <v>28417.27</v>
       </c>
       <c r="Q49" s="6">
-        <v>-0.1990719954634147</v>
+        <v>-0.27707263116146819</v>
       </c>
       <c r="R49" s="7">
         <v>317</v>
@@ -7897,7 +7889,7 @@
         <v>45208.25</v>
       </c>
       <c r="Q51" s="6">
-        <v>0.15873220920936859</v>
+        <v>0.038941713826089464</v>
       </c>
       <c r="R51" s="7">
         <v>496</v>
@@ -7933,7 +7925,7 @@
         <v>12.28333346456693</v>
       </c>
       <c r="AC51" s="8">
-        <v>16.223811999999999</v>
+        <v>16.635024999999999</v>
       </c>
       <c r="AD51" s="8">
         <v>23.416796874999999</v>
@@ -8028,7 +8020,7 @@
         <v>33150.599999999999</v>
       </c>
       <c r="Q52" s="6">
-        <v>0.45544444912753934</v>
+        <v>0.37655913782035033</v>
       </c>
       <c r="R52" s="7">
         <v>379</v>
@@ -8157,7 +8149,7 @@
         <v>37554.309999999998</v>
       </c>
       <c r="Q53" s="6">
-        <v>0.35978299557496651</v>
+        <v>0.23317176423148389</v>
       </c>
       <c r="R53" s="7">
         <v>383</v>
@@ -8288,7 +8280,7 @@
         <v>39237.149999999987</v>
       </c>
       <c r="Q54" s="6">
-        <v>0.17584505767573311</v>
+        <v>0.061154698060087442</v>
       </c>
       <c r="R54" s="7">
         <v>435</v>
@@ -8324,7 +8316,7 @@
         <v>7.5146970464135014</v>
       </c>
       <c r="AC54" s="8">
-        <v>13.204449</v>
+        <v>13.526273</v>
       </c>
       <c r="AD54" s="8">
         <v>20.375592887029288</v>
@@ -8376,7 +8368,7 @@
         <v>19649</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>44</v>
@@ -8411,59 +8403,59 @@
         <v>52</v>
       </c>
       <c r="O55" s="5">
-        <v>42766.519999999997</v>
+        <v>56863.669999999998</v>
       </c>
       <c r="P55" s="5">
-        <v>49894.273333333324</v>
+        <v>56863.669999999998</v>
       </c>
       <c r="Q55" s="6">
-        <v>-0.010911094423964429</v>
+        <v>0.0022818683824097352</v>
       </c>
       <c r="R55" s="7">
-        <v>557.66666666666674</v>
+        <v>648</v>
       </c>
       <c r="S55" s="6">
-        <v>-0.071844660194174459</v>
+        <v>-0.086036671368124096</v>
       </c>
       <c r="T55" s="6">
-        <v>0.22426919702608492</v>
+        <v>0.26662024980097138</v>
       </c>
       <c r="U55" s="6">
-        <v>-0.084793827040404501</v>
+        <v>-0.041662349616196068</v>
       </c>
       <c r="V55" s="6">
-        <v>0.043845290661947714</v>
+        <v>0.039548203624563807</v>
       </c>
       <c r="W55" s="6">
-        <v>0.0069853824907895245</v>
+        <v>0.0073443377819264917</v>
       </c>
       <c r="X55" s="8">
-        <v>23.778582710280372</v>
+        <v>23.621537676056338</v>
       </c>
       <c r="Y55" s="6">
-        <v>0.95327102803738317</v>
+        <v>0.96478873239436624</v>
       </c>
       <c r="Z55" s="6">
-        <v>0.032710280373831772</v>
+        <v>0.028169014084507043</v>
       </c>
       <c r="AA55" s="8">
-        <v>2.8212119047619044</v>
+        <v>2.7732693290734827</v>
       </c>
       <c r="AB55" s="8">
-        <v>5.9291868292682928</v>
+        <v>5.6407407407407408</v>
       </c>
       <c r="AC55" s="8">
-        <v>8.8212419999999998</v>
+        <v>8.5041429999999991</v>
       </c>
       <c r="AD55" s="8">
-        <v>16.334423831775702</v>
+        <v>15.886561267605634</v>
       </c>
       <c r="AE55" s="6">
-        <v>0.81775700934579443</v>
+        <v>0.83450704225352113</v>
       </c>
       <c r="AF55" s="9"/>
       <c r="AG55" s="5">
-        <v>-642</v>
+        <v>-695.39999999999998</v>
       </c>
       <c r="AH55" s="10">
         <v>5</v>
@@ -8546,7 +8538,7 @@
         <v>106458.58</v>
       </c>
       <c r="Q56" s="6">
-        <v>0.28250941505297744</v>
+        <v>0.14706480668586308</v>
       </c>
       <c r="R56" s="7">
         <v>1059</v>
@@ -8582,7 +8574,7 @@
         <v>7.6861251889168765</v>
       </c>
       <c r="AC56" s="8">
-        <v>13.046224</v>
+        <v>14.453963999999999</v>
       </c>
       <c r="AD56" s="8">
         <v>21.269503504380474</v>
@@ -8675,7 +8667,7 @@
         <v>34336</v>
       </c>
       <c r="Q57" s="6">
-        <v>-0.096530420001789241</v>
+        <v>-0.18604152240768235</v>
       </c>
       <c r="R57" s="7">
         <v>404</v>
@@ -8854,7 +8846,7 @@
         <v>19657</v>
       </c>
       <c r="B59" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C59" s="4">
         <v>44</v>
@@ -8891,59 +8883,59 @@
         <v>52</v>
       </c>
       <c r="O59" s="5">
-        <v>22795.139999999999</v>
+        <v>28958.02</v>
       </c>
       <c r="P59" s="5">
-        <v>26594.329999999998</v>
+        <v>28958.02</v>
       </c>
       <c r="Q59" s="6">
-        <v>-0.10069220884620578</v>
+        <v>-0.11411125149519252</v>
       </c>
       <c r="R59" s="7">
-        <v>287</v>
+        <v>312</v>
       </c>
       <c r="S59" s="6">
-        <v>-0.15753424657534232</v>
+        <v>-0.15902964959568733</v>
       </c>
       <c r="T59" s="6">
         <v>0</v>
       </c>
       <c r="U59" s="6">
-        <v>-0.31913469274590989</v>
+        <v>-0.32123674201482005</v>
       </c>
       <c r="V59" s="6">
-        <v>0.066537735675236048</v>
+        <v>0.062914177143326783</v>
       </c>
       <c r="W59" s="6">
-        <v>0.035961042573109885</v>
+        <v>0.034690217079758903</v>
       </c>
       <c r="X59" s="8">
-        <v>23.521905</v>
+        <v>23.797428571428572</v>
       </c>
       <c r="Y59" s="6">
-        <v>0.8571428571428571</v>
+        <v>0.85142857142857142</v>
       </c>
       <c r="Z59" s="6">
-        <v>0.021428571428571429</v>
+        <v>0.022857142857142857</v>
       </c>
       <c r="AA59" s="8">
-        <v>5.5829922131147542</v>
+        <v>5.7990864516129026</v>
       </c>
       <c r="AB59" s="8">
-        <v>5.9440478571428574</v>
+        <v>5.9505714285714282</v>
       </c>
       <c r="AC59" s="8">
-        <v>11.689807</v>
+        <v>11.860951</v>
       </c>
       <c r="AD59" s="8">
-        <v>18.595832857142856</v>
+        <v>18.801904571428569</v>
       </c>
       <c r="AE59" s="6">
-        <v>0.84999999999999998</v>
+        <v>0.85142857142857142</v>
       </c>
       <c r="AF59" s="9"/>
       <c r="AG59" s="5">
-        <v>-1081.5</v>
+        <v>-1506.1500000000001</v>
       </c>
       <c r="AH59" s="10">
         <v>3</v>
@@ -9119,7 +9111,7 @@
         <v>53410.209999999999</v>
       </c>
       <c r="Q61" s="6">
-        <v>0.20243570506333519</v>
+        <v>0.010326055395008193</v>
       </c>
       <c r="R61" s="7">
         <v>522</v>
@@ -9155,7 +9147,7 @@
         <v>3.5225138121546964</v>
       </c>
       <c r="AC61" s="8">
-        <v>7.137448</v>
+        <v>7.3951630000000002</v>
       </c>
       <c r="AD61" s="8">
         <v>15.115953743315506</v>
@@ -9250,7 +9242,7 @@
         <v>49913.970000000008</v>
       </c>
       <c r="Q62" s="6">
-        <v>0.17410765741459056</v>
+        <v>0.050139488500088536</v>
       </c>
       <c r="R62" s="7">
         <v>537</v>
@@ -9379,7 +9371,7 @@
         <v>51865.240000000005</v>
       </c>
       <c r="Q63" s="6">
-        <v>0.083908984250425034</v>
+        <v>-0.053360886399816621</v>
       </c>
       <c r="R63" s="7">
         <v>547</v>
@@ -9512,7 +9504,7 @@
         <v>10532.810000000001</v>
       </c>
       <c r="Q64" s="6">
-        <v>-0.29749138606055825</v>
+        <v>-0.35233444815230897</v>
       </c>
       <c r="R64" s="7">
         <v>139</v>
@@ -9643,7 +9635,7 @@
         <v>53741.830000000002</v>
       </c>
       <c r="Q65" s="6">
-        <v>0.49054765915159293</v>
+        <v>0.34249357066399222</v>
       </c>
       <c r="R65" s="7">
         <v>551</v>
@@ -9824,7 +9816,7 @@
         <v>19685</v>
       </c>
       <c r="B67" s="3">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c t="s" r="C67" s="4">
         <v>44</v>
@@ -9861,55 +9853,55 @@
         <v>52</v>
       </c>
       <c r="O67" s="5">
-        <v>6631.25</v>
+        <v>32449.449999999997</v>
       </c>
       <c r="P67" s="5">
-        <v>23209.375</v>
+        <v>32449.449999999993</v>
       </c>
       <c r="Q67" s="6">
-        <v>-0.14572765829952905</v>
+        <v>0.080616344724121936</v>
       </c>
       <c r="R67" s="7">
-        <v>213.5</v>
+        <v>331</v>
       </c>
       <c r="S67" s="6">
-        <v>-0.061538461538461542</v>
+        <v>0.034375000000000044</v>
       </c>
       <c r="T67" s="6">
         <v>0</v>
       </c>
       <c r="U67" s="6">
-        <v>-0.34390047125353435</v>
+        <v>-0.33555360722600847</v>
       </c>
       <c r="V67" s="6">
-        <v>0.032754231856738925</v>
+        <v>0.027797297026605997</v>
       </c>
       <c r="W67" s="6">
-        <v>-0.020205617342130062</v>
+        <v>-0.01033493633944489</v>
       </c>
       <c r="X67" s="8">
-        <v>30.845074999999998</v>
+        <v>35.167456896551727</v>
       </c>
       <c r="Y67" s="6">
-        <v>0.72727272727272729</v>
+        <v>0.37068965517241381</v>
       </c>
       <c r="Z67" s="6">
-        <v>0.13636363636363635</v>
+        <v>0.21551724137931033</v>
       </c>
       <c r="AA67" s="8">
-        <v>8.3833338709677427</v>
+        <v>7.2280076923076928</v>
       </c>
       <c r="AB67" s="8">
-        <v>6.604166666666667</v>
+        <v>13.152295918367347</v>
       </c>
       <c r="AC67" s="8">
-        <v>15.950091</v>
+        <v>20.246621000000001</v>
       </c>
       <c r="AD67" s="8">
-        <v>19.87575681818182</v>
+        <v>24.46277012987013</v>
       </c>
       <c r="AE67" s="6">
-        <v>0.43181818181818182</v>
+        <v>0.49137931034482757</v>
       </c>
       <c r="AF67" s="9"/>
       <c r="AG67" s="5">
@@ -9998,7 +9990,7 @@
         <v>34494.110000000001</v>
       </c>
       <c r="Q68" s="6">
-        <v>0.37730068453550292</v>
+        <v>0.24903626734374784</v>
       </c>
       <c r="R68" s="7">
         <v>447</v>
@@ -10129,7 +10121,7 @@
         <v>30531.870000000003</v>
       </c>
       <c r="Q69" s="6">
-        <v>-0.082760406637007122</v>
+        <v>-0.15045228063019056</v>
       </c>
       <c r="R69" s="7">
         <v>376</v>
@@ -10260,7 +10252,7 @@
         <v>42257.349999999999</v>
       </c>
       <c r="Q70" s="6">
-        <v>-0.062165087494210347</v>
+        <v>-0.11523110226798539</v>
       </c>
       <c r="R70" s="7">
         <v>402</v>
@@ -10389,7 +10381,7 @@
         <v>59626.440000000002</v>
       </c>
       <c r="Q71" s="6">
-        <v>0.20859391373898406</v>
+        <v>0.050513272353061245</v>
       </c>
       <c r="R71" s="7">
         <v>571</v>
@@ -10518,7 +10510,7 @@
         <v>27975.220000000001</v>
       </c>
       <c r="Q72" s="6">
-        <v>-0.49712731180306169</v>
+        <v>-0.14199009194205447</v>
       </c>
       <c r="R72" s="7">
         <v>262.5</v>
@@ -10604,7 +10596,7 @@
         <v>19694</v>
       </c>
       <c r="B73" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C73" s="4">
         <v>44</v>
@@ -10641,59 +10633,59 @@
         <v>52</v>
       </c>
       <c r="O73" s="5">
-        <v>32788.300000000003</v>
+        <v>40742.260000000002</v>
       </c>
       <c r="P73" s="5">
-        <v>38253.01666666667</v>
+        <v>40742.260000000002</v>
       </c>
       <c r="Q73" s="6">
-        <v>0.13160979333750844</v>
+        <v>0.088558135906185109</v>
       </c>
       <c r="R73" s="7">
-        <v>411.83333333333337</v>
+        <v>439</v>
       </c>
       <c r="S73" s="6">
-        <v>-0.0056338028169011789</v>
+        <v>-0.022271714922049046</v>
       </c>
       <c r="T73" s="6">
-        <v>9.1674329745671468</v>
+        <v>7.3812324745853557</v>
       </c>
       <c r="U73" s="6">
-        <v>4.3357353873180369</v>
+        <v>2.4110469718665581</v>
       </c>
       <c r="V73" s="6">
-        <v>0.10765927175242387</v>
+        <v>0.10689891773308599</v>
       </c>
       <c r="W73" s="6">
-        <v>0.071443304471412047</v>
+        <v>0.071941112250523173</v>
       </c>
       <c r="X73" s="8">
-        <v>57.173478260869565</v>
+        <v>53.220093031358886</v>
       </c>
       <c r="Y73" s="6">
-        <v>0.43722943722943725</v>
+        <v>0.44444444444444442</v>
       </c>
       <c r="Z73" s="6">
-        <v>0.56086956521739129</v>
+        <v>0.49477351916376305</v>
       </c>
       <c r="AA73" s="8">
-        <v>13.176217415730337</v>
+        <v>12.275075565610861</v>
       </c>
       <c r="AB73" s="8">
-        <v>24.204128828828829</v>
+        <v>22.372382310469316</v>
       </c>
       <c r="AC73" s="8">
-        <v>38.334485000000001</v>
+        <v>35.260669999999998</v>
       </c>
       <c r="AD73" s="8">
-        <v>42.992708482142859</v>
+        <v>40.205575444839859</v>
       </c>
       <c r="AE73" s="6">
-        <v>0.24782608695652175</v>
+        <v>0.26132404181184671</v>
       </c>
       <c r="AF73" s="9"/>
       <c r="AG73" s="5">
-        <v>-1393.03</v>
+        <v>-1905.71</v>
       </c>
       <c r="AH73" s="10">
         <v>2</v>
@@ -10778,7 +10770,7 @@
         <v>39192.269999999997</v>
       </c>
       <c r="Q74" s="6">
-        <v>-0.15829802642091007</v>
+        <v>-0.24522098876678888</v>
       </c>
       <c r="R74" s="7">
         <v>456</v>
@@ -10909,7 +10901,7 @@
         <v>35087.830000000002</v>
       </c>
       <c r="Q75" s="6">
-        <v>0.15373660823205326</v>
+        <v>0.044064384282303415</v>
       </c>
       <c r="R75" s="7">
         <v>404</v>
@@ -10997,7 +10989,7 @@
         <v>19706</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -11035,28 +11027,28 @@
         <v>31868.620000000003</v>
       </c>
       <c r="P76" s="5">
-        <v>37180.056666666671</v>
+        <v>31868.620000000003</v>
       </c>
       <c r="Q76" s="6">
-        <v>-0.020464652431020469</v>
+        <v>-0.24844506053498305</v>
       </c>
       <c r="R76" s="7">
-        <v>410.66666666666663</v>
+        <v>352</v>
       </c>
       <c r="S76" s="6">
-        <v>-0.14146341463414636</v>
+        <v>-0.34693877551020413</v>
       </c>
       <c r="T76" s="6">
-        <v>-0.00025040306106759565</v>
+        <v>0.00016681299660920365</v>
       </c>
       <c r="U76" s="6">
-        <v>-0.33624016352135738</v>
+        <v>-0.33582294746368063</v>
       </c>
       <c r="V76" s="6">
-        <v>0.013965195229664792</v>
+        <v>0.035765841131495495</v>
       </c>
       <c r="W76" s="6">
-        <v>-0.011949952649345973</v>
+        <v>0.0062465208722561573</v>
       </c>
       <c r="X76" s="8">
         <v>22.956818181818182</v>
@@ -11115,7 +11107,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR76" s="4">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c t="s" r="AS76" s="4">
         <v>56</v>
@@ -11135,7 +11127,7 @@
         <v>148</v>
       </c>
       <c t="s" r="E77" s="4">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c t="s" r="F77" s="4">
         <v>47</v>
@@ -11262,7 +11254,7 @@
         <v>27421.639999999996</v>
       </c>
       <c r="Q78" s="6">
-        <v>-0.23930626217120399</v>
+        <v>-0.30602459643897018</v>
       </c>
       <c r="R78" s="7">
         <v>293</v>
@@ -11339,7 +11331,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR78" s="4">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c t="s" r="AS78" s="4">
         <v>56</v>
@@ -11393,7 +11385,7 @@
         <v>44631.349999999991</v>
       </c>
       <c r="Q79" s="6">
-        <v>0.44033008798236906</v>
+        <v>0.29464287009262358</v>
       </c>
       <c r="R79" s="7">
         <v>465</v>
@@ -11470,7 +11462,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR79" s="4">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c t="s" r="AS79" s="4">
         <v>56</v>
@@ -11522,7 +11514,7 @@
         <v>32254.77</v>
       </c>
       <c r="Q80" s="6">
-        <v>-0.02452982486170785</v>
+        <v>-0.1170624014540993</v>
       </c>
       <c r="R80" s="7">
         <v>358</v>
@@ -11599,7 +11591,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR80" s="4">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c t="s" r="AS80" s="4">
         <v>56</v>
@@ -11694,7 +11686,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR81" s="4">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c t="s" r="AS81" s="4">
         <v>56</v>
@@ -11714,7 +11706,7 @@
         <v>99</v>
       </c>
       <c t="s" r="E82" s="4">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c t="s" r="F82" s="4">
         <v>47</v>
@@ -11748,7 +11740,7 @@
         <v>36335.510000000002</v>
       </c>
       <c r="Q82" s="6">
-        <v>0.24900821511720461</v>
+        <v>0.19005503292706871</v>
       </c>
       <c r="R82" s="7">
         <v>383</v>
@@ -11784,7 +11776,7 @@
         <v>8.667852434456929</v>
       </c>
       <c r="AC82" s="8">
-        <v>16.012692000000001</v>
+        <v>16.040496000000001</v>
       </c>
       <c r="AD82" s="8">
         <v>20.751764233576644</v>
@@ -11879,7 +11871,7 @@
         <v>36225.889999999999</v>
       </c>
       <c r="Q83" s="6">
-        <v>-0.0086937271351829049</v>
+        <v>-0.078194185424858897</v>
       </c>
       <c r="R83" s="7">
         <v>415</v>
@@ -12008,7 +12000,7 @@
         <v>37618.82</v>
       </c>
       <c r="Q84" s="6">
-        <v>0.1349464036275978</v>
+        <v>0.013543434204095428</v>
       </c>
       <c r="R84" s="7">
         <v>341</v>
@@ -12085,7 +12077,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR84" s="4">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c t="s" r="AS84" s="4">
         <v>56</v>
@@ -12139,7 +12131,7 @@
         <v>19484.939999999999</v>
       </c>
       <c r="Q85" s="6">
-        <v>0.13849745918837764</v>
+        <v>0.076793251743266344</v>
       </c>
       <c r="R85" s="7">
         <v>255</v>
@@ -12175,7 +12167,7 @@
         <v>3.0839872549019609</v>
       </c>
       <c r="AC85" s="8">
-        <v>6.319483</v>
+        <v>8.4116</v>
       </c>
       <c r="AD85" s="8">
         <v>15.32205882352941</v>
@@ -12270,7 +12262,7 @@
         <v>27871.27</v>
       </c>
       <c r="Q86" s="6">
-        <v>-0.15563610695394525</v>
+        <v>-0.23469157718567712</v>
       </c>
       <c r="R86" s="7">
         <v>336</v>
@@ -12440,7 +12432,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR87" s="4">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c t="s" r="AS87" s="4">
         <v>56</v>
@@ -12451,14 +12443,14 @@
         <v>19730</v>
       </c>
       <c r="B88" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C88" s="4">
         <v>44</v>
       </c>
       <c r="D88" s="4"/>
       <c t="s" r="E88" s="4">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c t="s" r="F88" s="4">
         <v>47</v>
@@ -12486,55 +12478,55 @@
         <v>52</v>
       </c>
       <c r="O88" s="5">
-        <v>49823.050000000003</v>
+        <v>64593.040000000001</v>
       </c>
       <c r="P88" s="5">
-        <v>58126.89166666667</v>
+        <v>64593.040000000001</v>
       </c>
       <c r="Q88" s="6">
-        <v>0.064945386186860521</v>
+        <v>0.050863704560296208</v>
       </c>
       <c r="R88" s="7">
-        <v>564.66666666666674</v>
+        <v>640</v>
       </c>
       <c r="S88" s="6">
-        <v>-0.083333333333333259</v>
+        <v>-0.09219858156028371</v>
       </c>
       <c r="T88" s="6">
-        <v>0.0035844854941638458</v>
+        <v>0.017648650690538795</v>
       </c>
       <c r="U88" s="6">
-        <v>-0.33072202524735039</v>
+        <v>-0.31556062386907319</v>
       </c>
       <c r="V88" s="6">
-        <v>0.026036583468896424</v>
+        <v>0.029167492349020885</v>
       </c>
       <c r="W88" s="6">
-        <v>0.010818928186853274</v>
+        <v>0.01358996263374506</v>
       </c>
       <c r="X88" s="8">
-        <v>30.670779870129874</v>
+        <v>32.490306632653059</v>
       </c>
       <c r="Y88" s="6">
-        <v>0.58441558441558439</v>
+        <v>0.54081632653061229</v>
       </c>
       <c r="Z88" s="6">
-        <v>0.20129870129870131</v>
+        <v>0.23979591836734693</v>
       </c>
       <c r="AA88" s="8">
-        <v>7.5410701431492839</v>
+        <v>8.0618086821705432</v>
       </c>
       <c r="AB88" s="8">
-        <v>9.3876908496732039</v>
+        <v>10.039658461538462</v>
       </c>
       <c r="AC88" s="8">
-        <v>13.394824</v>
+        <v>17.879843999999999</v>
       </c>
       <c r="AD88" s="8">
-        <v>24.697185714285713</v>
+        <v>25.700509693877549</v>
       </c>
       <c r="AE88" s="6">
-        <v>0.57792207792207795</v>
+        <v>0.49489795918367346</v>
       </c>
       <c r="AF88" s="9"/>
       <c r="AG88" s="5">
@@ -12569,7 +12561,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR88" s="4">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c t="s" r="AS88" s="4">
         <v>56</v>
@@ -12589,7 +12581,7 @@
         <v>148</v>
       </c>
       <c t="s" r="E89" s="4">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c t="s" r="F89" s="4">
         <v>47</v>
@@ -12662,7 +12654,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR89" s="4">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c t="s" r="AS89" s="4">
         <v>56</v>
@@ -12716,7 +12708,7 @@
         <v>16998.790000000001</v>
       </c>
       <c r="Q90" s="6">
-        <v>-0.14829235492883219</v>
+        <v>-0.19857402025771931</v>
       </c>
       <c r="R90" s="7">
         <v>193</v>
@@ -12793,7 +12785,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR90" s="4">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c t="s" r="AS90" s="4">
         <v>56</v>
@@ -12811,7 +12803,7 @@
       </c>
       <c r="D91" s="4"/>
       <c t="s" r="E91" s="4">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c t="s" r="F91" s="4">
         <v>47</v>
@@ -12845,7 +12837,7 @@
         <v>51845.590000000004</v>
       </c>
       <c r="Q91" s="6">
-        <v>-0.13526462319349164</v>
+        <v>-0.23459655082969544</v>
       </c>
       <c r="R91" s="7">
         <v>566</v>
@@ -12922,7 +12914,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR91" s="4">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c t="s" r="AS91" s="4">
         <v>56</v>
@@ -12940,7 +12932,7 @@
       </c>
       <c r="D92" s="4"/>
       <c t="s" r="E92" s="4">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c t="s" r="F92" s="4">
         <v>47</v>
@@ -12974,7 +12966,7 @@
         <v>81884.610000000001</v>
       </c>
       <c r="Q92" s="6">
-        <v>-0.075409501766593223</v>
+        <v>-0.14650979368650852</v>
       </c>
       <c r="R92" s="7">
         <v>766</v>
@@ -13010,7 +13002,7 @@
         <v>2.0092033670033667</v>
       </c>
       <c r="AC92" s="8">
-        <v>4.9173489999999997</v>
+        <v>5.3671030000000002</v>
       </c>
       <c r="AD92" s="8">
         <v>14.855812962962963</v>
@@ -13105,7 +13097,7 @@
         <v>54606.900000000001</v>
       </c>
       <c r="Q93" s="6">
-        <v>0.30899595676832026</v>
+        <v>0.17402406531220893</v>
       </c>
       <c r="R93" s="7">
         <v>482</v>
@@ -13182,7 +13174,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR93" s="4">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c t="s" r="AS93" s="4">
         <v>56</v>
@@ -13202,7 +13194,7 @@
         <v>125</v>
       </c>
       <c t="s" r="E94" s="4">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c t="s" r="F94" s="4">
         <v>47</v>
@@ -13236,7 +13228,7 @@
         <v>28023.27</v>
       </c>
       <c r="Q94" s="6">
-        <v>-0.0040405928714399852</v>
+        <v>-0.095904557761150255</v>
       </c>
       <c r="R94" s="7">
         <v>319</v>
@@ -13313,7 +13305,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR94" s="4">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c t="s" r="AS94" s="4">
         <v>56</v>
@@ -13331,7 +13323,7 @@
       </c>
       <c r="D95" s="4"/>
       <c t="s" r="E95" s="4">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c t="s" r="F95" s="4">
         <v>47</v>
@@ -13365,7 +13357,7 @@
         <v>21202.580000000002</v>
       </c>
       <c r="Q95" s="6">
-        <v>-0.34860564806926542</v>
+        <v>-0.065712928518991465</v>
       </c>
       <c r="R95" s="7">
         <v>175</v>
@@ -13442,7 +13434,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR95" s="4">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c t="s" r="AS95" s="4">
         <v>56</v>
@@ -13462,7 +13454,7 @@
         <v>45</v>
       </c>
       <c t="s" r="E96" s="4">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c t="s" r="F96" s="4">
         <v>47</v>
@@ -13496,7 +13488,7 @@
         <v>43264.379999999997</v>
       </c>
       <c r="Q96" s="6">
-        <v>0.24358308829235908</v>
+        <v>0.12061328587483833</v>
       </c>
       <c r="R96" s="7">
         <v>503</v>
@@ -13532,7 +13524,7 @@
         <v>15.648298775510204</v>
       </c>
       <c r="AC96" s="8">
-        <v>27.000966999999999</v>
+        <v>25.719321000000001</v>
       </c>
       <c r="AD96" s="8">
         <v>29.051248314606742</v>
@@ -13573,7 +13565,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR96" s="4">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c t="s" r="AS96" s="4">
         <v>56</v>
@@ -13591,7 +13583,7 @@
       </c>
       <c r="D97" s="4"/>
       <c t="s" r="E97" s="4">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c t="s" r="F97" s="4">
         <v>47</v>
@@ -13625,7 +13617,7 @@
         <v>28014.600000000006</v>
       </c>
       <c r="Q97" s="6">
-        <v>0.10089817912024368</v>
+        <v>-0.0011185207714332623</v>
       </c>
       <c r="R97" s="7">
         <v>295</v>
@@ -13702,7 +13694,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR97" s="4">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c t="s" r="AS97" s="4">
         <v>56</v>
@@ -13720,7 +13712,7 @@
       </c>
       <c r="D98" s="4"/>
       <c t="s" r="E98" s="4">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c t="s" r="F98" s="4">
         <v>47</v>
@@ -13754,7 +13746,7 @@
         <v>18453.540000000001</v>
       </c>
       <c r="Q98" s="6">
-        <v>-0.047967064431752915</v>
+        <v>-0.13290345498705702</v>
       </c>
       <c r="R98" s="7">
         <v>231</v>
@@ -13831,7 +13823,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR98" s="4">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c t="s" r="AS98" s="4">
         <v>56</v>
@@ -13885,7 +13877,7 @@
         <v>48937.5</v>
       </c>
       <c r="Q99" s="6">
-        <v>0.049699842150883411</v>
+        <v>-0.0631997287849555</v>
       </c>
       <c r="R99" s="7">
         <v>571</v>
@@ -13921,7 +13913,7 @@
         <v>5.1992232974910397</v>
       </c>
       <c r="AC99" s="8">
-        <v>9.716412</v>
+        <v>9.5417670000000001</v>
       </c>
       <c r="AD99" s="8">
         <v>16.405357500000001</v>
@@ -13962,7 +13954,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR99" s="4">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c t="s" r="AS99" s="4">
         <v>56</v>
@@ -14016,7 +14008,7 @@
         <v>64609.930000000008</v>
       </c>
       <c r="Q100" s="6">
-        <v>0.17061480081952207</v>
+        <v>0.045344305496501258</v>
       </c>
       <c r="R100" s="7">
         <v>571</v>
@@ -14052,7 +14044,7 @@
         <v>6.9379409556314</v>
       </c>
       <c r="AC100" s="8">
-        <v>10.301113000000001</v>
+        <v>10.302593</v>
       </c>
       <c r="AD100" s="8">
         <v>18.157432094594594</v>
@@ -14147,7 +14139,7 @@
         <v>19609.950000000001</v>
       </c>
       <c r="Q101" s="6">
-        <v>-0.29731297673816937</v>
+        <v>-0.35864327687352027</v>
       </c>
       <c r="R101" s="7">
         <v>160</v>
@@ -14278,7 +14270,7 @@
         <v>39443.040000000001</v>
       </c>
       <c r="Q102" s="6">
-        <v>-0.17043684995570674</v>
+        <v>-0.29264439146461174</v>
       </c>
       <c r="R102" s="7">
         <v>443</v>
@@ -14375,7 +14367,7 @@
         <v>80</v>
       </c>
       <c t="s" r="E103" s="4">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c t="s" r="F103" s="4">
         <v>47</v>
@@ -14409,7 +14401,7 @@
         <v>22133.889999999996</v>
       </c>
       <c r="Q103" s="6">
-        <v>-0.34779819655021427</v>
+        <v>-0.40888540401176898</v>
       </c>
       <c r="R103" s="7">
         <v>258</v>
@@ -14486,7 +14478,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR103" s="4">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c t="s" r="AS103" s="4">
         <v>56</v>
@@ -14506,7 +14498,7 @@
         <v>89</v>
       </c>
       <c t="s" r="E104" s="4">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c t="s" r="F104" s="4">
         <v>47</v>
@@ -14540,7 +14532,7 @@
         <v>27720.100000000002</v>
       </c>
       <c r="Q104" s="6">
-        <v>0.07289215382709946</v>
+        <v>-0.025163492012136746</v>
       </c>
       <c r="R104" s="7">
         <v>306</v>
@@ -14617,7 +14609,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR104" s="4">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c t="s" r="AS104" s="4">
         <v>56</v>
@@ -14634,10 +14626,10 @@
         <v>44</v>
       </c>
       <c t="s" r="D105" s="4">
+        <v>187</v>
+      </c>
+      <c t="s" r="E105" s="4">
         <v>188</v>
-      </c>
-      <c t="s" r="E105" s="4">
-        <v>189</v>
       </c>
       <c t="s" r="F105" s="4">
         <v>47</v>
@@ -14655,10 +14647,10 @@
         <v>47</v>
       </c>
       <c t="s" r="K105" s="4">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c t="s" r="L105" s="4">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="M105" s="4"/>
       <c t="s" r="N105" s="4">
@@ -14671,7 +14663,7 @@
         <v>21745.450000000004</v>
       </c>
       <c r="Q105" s="6">
-        <v>-0.094889195419139205</v>
+        <v>-0.17557234833233615</v>
       </c>
       <c r="R105" s="7">
         <v>286</v>
@@ -14748,7 +14740,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR105" s="4">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c t="s" r="AS105" s="4">
         <v>56</v>
@@ -14802,7 +14794,7 @@
         <v>24075.950000000004</v>
       </c>
       <c r="Q106" s="6">
-        <v>-0.074817862554293346</v>
+        <v>-0.15684985620611047</v>
       </c>
       <c r="R106" s="7">
         <v>242</v>
@@ -14879,7 +14871,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR106" s="4">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c t="s" r="AS106" s="4">
         <v>56</v>
@@ -14933,7 +14925,7 @@
         <v>32193.079999999998</v>
       </c>
       <c r="Q107" s="6">
-        <v>-0.19595975338131644</v>
+        <v>-0.24390448977712942</v>
       </c>
       <c r="R107" s="7">
         <v>297</v>
@@ -15030,7 +15022,7 @@
         <v>70</v>
       </c>
       <c t="s" r="E108" s="4">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c t="s" r="F108" s="4">
         <v>47</v>
@@ -15064,7 +15056,7 @@
         <v>24102.920000000002</v>
       </c>
       <c r="Q108" s="6">
-        <v>0.078071068033250812</v>
+        <v>-0.019250472615175207</v>
       </c>
       <c r="R108" s="7">
         <v>231</v>
@@ -15098,7 +15090,7 @@
         <v>11.774294915254238</v>
       </c>
       <c r="AC108" s="8">
-        <v>17.897500000000001</v>
+        <v>18.337954</v>
       </c>
       <c r="AD108" s="8">
         <v>24.823162711864409</v>
@@ -15139,7 +15131,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR108" s="4">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c t="s" r="AS108" s="4">
         <v>56</v>
@@ -15193,7 +15185,7 @@
         <v>66077.920000000013</v>
       </c>
       <c r="Q109" s="6">
-        <v>0.051915444222210949</v>
+        <v>-0.15107488505490163</v>
       </c>
       <c r="R109" s="7">
         <v>850</v>
@@ -15270,7 +15262,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR109" s="4">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c t="s" r="AS109" s="4">
         <v>56</v>
@@ -15290,7 +15282,7 @@
         <v>94</v>
       </c>
       <c t="s" r="E110" s="4">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c t="s" r="F110" s="4">
         <v>47</v>
@@ -15324,7 +15316,7 @@
         <v>32370.59</v>
       </c>
       <c r="Q110" s="6">
-        <v>0.20769650919765192</v>
+        <v>0.14827765039076901</v>
       </c>
       <c r="R110" s="7">
         <v>338</v>
@@ -15401,7 +15393,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR110" s="4">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c t="s" r="AS110" s="4">
         <v>56</v>
@@ -15421,7 +15413,7 @@
         <v>125</v>
       </c>
       <c t="s" r="E111" s="4">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c t="s" r="F111" s="4">
         <v>47</v>
@@ -15455,7 +15447,7 @@
         <v>29955.209999999999</v>
       </c>
       <c r="Q111" s="6">
-        <v>0.85377640475721917</v>
+        <v>0.68693128766777689</v>
       </c>
       <c r="R111" s="7">
         <v>352</v>
@@ -15491,7 +15483,7 @@
         <v>12.80994537815126</v>
       </c>
       <c r="AC111" s="8">
-        <v>21.480844999999999</v>
+        <v>25.178795000000001</v>
       </c>
       <c r="AD111" s="8">
         <v>32.09779752066116</v>
@@ -15532,7 +15524,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR111" s="4">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c t="s" r="AS111" s="4">
         <v>56</v>
@@ -15552,7 +15544,7 @@
         <v>80</v>
       </c>
       <c t="s" r="E112" s="4">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c t="s" r="F112" s="4">
         <v>47</v>
@@ -15586,7 +15578,7 @@
         <v>22487.579999999998</v>
       </c>
       <c r="Q112" s="6">
-        <v>0.0038641097592877482</v>
+        <v>-0.043518427543508764</v>
       </c>
       <c r="R112" s="7">
         <v>348</v>
@@ -15680,10 +15672,10 @@
         <v>44</v>
       </c>
       <c t="s" r="D113" s="4">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c t="s" r="E113" s="4">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c t="s" r="F113" s="4">
         <v>47</v>
@@ -15717,7 +15709,7 @@
         <v>34222.879999999997</v>
       </c>
       <c r="Q113" s="6">
-        <v>-0.021328216376359399</v>
+        <v>-0.12083833418279277</v>
       </c>
       <c r="R113" s="7">
         <v>322</v>
@@ -15794,7 +15786,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR113" s="4">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c t="s" r="AS113" s="4">
         <v>56</v>
@@ -15812,7 +15804,7 @@
       </c>
       <c r="D114" s="4"/>
       <c t="s" r="E114" s="4">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c t="s" r="F114" s="4">
         <v>47</v>
@@ -15846,7 +15838,7 @@
         <v>19094.09</v>
       </c>
       <c r="Q114" s="6">
-        <v>0.24597965618588713</v>
+        <v>0.13980685337427579</v>
       </c>
       <c r="R114" s="7">
         <v>202</v>
@@ -15923,7 +15915,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR114" s="4">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c t="s" r="AS114" s="4">
         <v>56</v>
@@ -15975,7 +15967,7 @@
         <v>106571.76000000001</v>
       </c>
       <c r="Q115" s="6">
-        <v>0.13347045649590594</v>
+        <v>0.010749025023141456</v>
       </c>
       <c r="R115" s="7">
         <v>1024</v>
@@ -16106,7 +16098,7 @@
         <v>58354.599999999999</v>
       </c>
       <c r="Q116" s="6">
-        <v>-0.049459708901861577</v>
+        <v>-0.12255569828460011</v>
       </c>
       <c r="R116" s="7">
         <v>577</v>
@@ -16200,10 +16192,10 @@
         <v>44</v>
       </c>
       <c t="s" r="D117" s="4">
+        <v>202</v>
+      </c>
+      <c t="s" r="E117" s="4">
         <v>203</v>
-      </c>
-      <c t="s" r="E117" s="4">
-        <v>204</v>
       </c>
       <c t="s" r="F117" s="4">
         <v>47</v>
@@ -16294,7 +16286,7 @@
       </c>
       <c r="D118" s="4"/>
       <c t="s" r="E118" s="4">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c t="s" r="F118" s="4">
         <v>47</v>
@@ -16328,7 +16320,7 @@
         <v>63278.479999999996</v>
       </c>
       <c r="Q118" s="6">
-        <v>0.11625980477332476</v>
+        <v>-0.012556038556805649</v>
       </c>
       <c r="R118" s="7">
         <v>628</v>
@@ -16405,7 +16397,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR118" s="4">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c t="s" r="AS118" s="4">
         <v>56</v>
@@ -16423,7 +16415,7 @@
       </c>
       <c r="D119" s="4"/>
       <c t="s" r="E119" s="4">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c t="s" r="F119" s="4">
         <v>47</v>
@@ -16457,7 +16449,7 @@
         <v>52781.880000000005</v>
       </c>
       <c r="Q119" s="6">
-        <v>-0.04759440442847418</v>
+        <v>-0.093711962112396519</v>
       </c>
       <c r="R119" s="7">
         <v>646</v>
@@ -16493,7 +16485,7 @@
         <v>9.0862323369565221</v>
       </c>
       <c r="AC119" s="8">
-        <v>20.993676000000001</v>
+        <v>20.133966000000001</v>
       </c>
       <c r="AD119" s="8">
         <v>27.680425260416666</v>
@@ -16534,7 +16526,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR119" s="4">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c t="s" r="AS119" s="4">
         <v>56</v>
@@ -16554,7 +16546,7 @@
         <v>86</v>
       </c>
       <c t="s" r="E120" s="4">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c t="s" r="F120" s="4">
         <v>47</v>
@@ -16588,7 +16580,7 @@
         <v>55386.330000000002</v>
       </c>
       <c r="Q120" s="6">
-        <v>0.29621309386009709</v>
+        <v>0.1213137833759228</v>
       </c>
       <c r="R120" s="7">
         <v>704</v>
@@ -16665,7 +16657,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR120" s="4">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c t="s" r="AS120" s="4">
         <v>56</v>
@@ -16719,7 +16711,7 @@
         <v>49345.87000000001</v>
       </c>
       <c r="Q121" s="6">
-        <v>0.044922290237851659</v>
+        <v>-0.15036595862495461</v>
       </c>
       <c r="R121" s="7">
         <v>599</v>
@@ -16850,7 +16842,7 @@
         <v>26197.420000000002</v>
       </c>
       <c r="Q122" s="6">
-        <v>0.18130433351415376</v>
+        <v>-0.28740156944860396</v>
       </c>
       <c r="R122" s="7">
         <v>327</v>
@@ -16886,7 +16878,7 @@
         <v>10.751754736842106</v>
       </c>
       <c r="AC122" s="8">
-        <v>17.816320000000001</v>
+        <v>18.066216000000001</v>
       </c>
       <c r="AD122" s="8">
         <v>24.639862886597935</v>
@@ -16945,7 +16937,7 @@
         <v>89</v>
       </c>
       <c t="s" r="E123" s="4">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c t="s" r="F123" s="4">
         <v>47</v>
@@ -16979,7 +16971,7 @@
         <v>28211.34</v>
       </c>
       <c r="Q123" s="6">
-        <v>-0.041172236168351306</v>
+        <v>-0.21045441913223517</v>
       </c>
       <c r="R123" s="7">
         <v>316</v>
@@ -17015,7 +17007,7 @@
         <v>2.249295</v>
       </c>
       <c r="AC123" s="8">
-        <v>7.3914669999999996</v>
+        <v>7.2579789999999997</v>
       </c>
       <c r="AD123" s="8">
         <v>14.144677186311787</v>
@@ -17058,7 +17050,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR123" s="4">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c t="s" r="AS123" s="4">
         <v>56</v>
@@ -17078,7 +17070,7 @@
         <v>89</v>
       </c>
       <c t="s" r="E124" s="4">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c t="s" r="F124" s="4">
         <v>47</v>
@@ -17112,7 +17104,7 @@
         <v>17177.509999999998</v>
       </c>
       <c r="Q124" s="6">
-        <v>-0.3073031637203294</v>
+        <v>-0.3289415213553909</v>
       </c>
       <c r="R124" s="7">
         <v>182</v>
@@ -17189,7 +17181,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR124" s="4">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c t="s" r="AS124" s="4">
         <v>56</v>
@@ -17209,7 +17201,7 @@
         <v>68</v>
       </c>
       <c t="s" r="E125" s="4">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c t="s" r="F125" s="4">
         <v>47</v>
@@ -17243,7 +17235,7 @@
         <v>70401.270000000004</v>
       </c>
       <c r="Q125" s="6">
-        <v>0.067808564185891873</v>
+        <v>0.011720077050291433</v>
       </c>
       <c r="R125" s="7">
         <v>661</v>
@@ -17337,10 +17329,10 @@
         <v>44</v>
       </c>
       <c t="s" r="D126" s="4">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c t="s" r="E126" s="4">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c t="s" r="F126" s="4">
         <v>47</v>
@@ -17415,7 +17407,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR126" s="4">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c t="s" r="AS126" s="4">
         <v>56</v>
@@ -17469,7 +17461,7 @@
         <v>29780.380000000001</v>
       </c>
       <c r="Q127" s="6">
-        <v>0.22075352899027179</v>
+        <v>0.15471108745021889</v>
       </c>
       <c r="R127" s="7">
         <v>320</v>
@@ -17505,7 +17497,7 @@
         <v>6.237108547008547</v>
       </c>
       <c r="AC127" s="8">
-        <v>11.745374</v>
+        <v>12.589532</v>
       </c>
       <c r="AD127" s="8">
         <v>19.248478838174272</v>
@@ -17546,7 +17538,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR127" s="4">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c t="s" r="AS127" s="4">
         <v>56</v>
@@ -17600,7 +17592,7 @@
         <v>26067.539999999997</v>
       </c>
       <c r="Q128" s="6">
-        <v>-0.2408425084441308</v>
+        <v>-0.2944702303026433</v>
       </c>
       <c r="R128" s="7">
         <v>288</v>
@@ -17636,7 +17628,7 @@
         <v>3.7985232067510548</v>
       </c>
       <c r="AC128" s="8">
-        <v>9.1770329999999998</v>
+        <v>9.1706090000000007</v>
       </c>
       <c r="AD128" s="8">
         <v>16.167018565400845</v>
@@ -17677,7 +17669,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR128" s="4">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c t="s" r="AS128" s="4">
         <v>56</v>
@@ -17688,7 +17680,7 @@
         <v>19863</v>
       </c>
       <c r="B129" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c t="s" r="C129" s="4">
         <v>44</v>
@@ -17725,55 +17717,55 @@
         <v>52</v>
       </c>
       <c r="O129" s="5">
-        <v>20497.199999999997</v>
+        <v>39194.859999999993</v>
       </c>
       <c r="P129" s="5">
-        <v>35870.099999999991</v>
+        <v>45727.336666666662</v>
       </c>
       <c r="Q129" s="6">
-        <v>-0.349007561436673</v>
+        <v>-0.22321735227055406</v>
       </c>
       <c r="R129" s="7">
-        <v>393.75</v>
+        <v>507.5</v>
       </c>
       <c r="S129" s="6">
-        <v>0.0044642857142858094</v>
+        <v>-0.10123966942148777</v>
       </c>
       <c r="T129" s="6">
-        <v>0.32451590461136154</v>
+        <v>0.30832400728054649</v>
       </c>
       <c r="U129" s="6">
-        <v>0.011448266104638682</v>
+        <v>-0.0013109805724526122</v>
       </c>
       <c r="V129" s="6">
-        <v>0.050355219249458467</v>
+        <v>0.0440544244832103</v>
       </c>
       <c r="W129" s="6">
-        <v>0.020692631188650158</v>
+        <v>0.015701216945283133</v>
       </c>
       <c r="X129" s="8">
-        <v>26.094791874999999</v>
+        <v>30.539698058252426</v>
       </c>
       <c r="Y129" s="6">
-        <v>0.73750000000000004</v>
+        <v>0.59223300970873782</v>
       </c>
       <c r="Z129" s="6">
-        <v>0.056250000000000001</v>
+        <v>0.13268608414239483</v>
       </c>
       <c r="AA129" s="8">
-        <v>4.9733739837398376</v>
+        <v>5.1910765486725658</v>
       </c>
       <c r="AB129" s="8">
-        <v>4.5002378571428574</v>
+        <v>5.3286568345323744</v>
       </c>
       <c r="AC129" s="8">
-        <v>9.8025020000000005</v>
+        <v>10.816316</v>
       </c>
       <c r="AD129" s="8">
-        <v>15.62177125</v>
+        <v>16.930890553745929</v>
       </c>
       <c r="AE129" s="6">
-        <v>0.72499999999999998</v>
+        <v>0.60517799352750812</v>
       </c>
       <c r="AF129" s="9"/>
       <c r="AG129" s="5">
@@ -17824,7 +17816,7 @@
       </c>
       <c r="D130" s="4"/>
       <c t="s" r="E130" s="4">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c t="s" r="F130" s="4">
         <v>47</v>
@@ -17858,7 +17850,7 @@
         <v>26469.079999999998</v>
       </c>
       <c r="Q130" s="6">
-        <v>-0.26501421012660686</v>
+        <v>-0.33021006880831449</v>
       </c>
       <c r="R130" s="7">
         <v>279</v>
@@ -17950,10 +17942,10 @@
         <v>44</v>
       </c>
       <c t="s" r="D131" s="4">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c t="s" r="E131" s="4">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c t="s" r="F131" s="4">
         <v>47</v>
@@ -17987,7 +17979,7 @@
         <v>24765.5</v>
       </c>
       <c r="Q131" s="6">
-        <v>-0.012781953388622869</v>
+        <v>-0.09920674324618739</v>
       </c>
       <c r="R131" s="7">
         <v>332</v>
@@ -18050,7 +18042,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR131" s="4">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c t="s" r="AS131" s="4">
         <v>56</v>
@@ -18061,7 +18053,7 @@
         <v>19872</v>
       </c>
       <c r="B132" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C132" s="4">
         <v>44</v>
@@ -18070,7 +18062,7 @@
         <v>94</v>
       </c>
       <c t="s" r="E132" s="4">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c t="s" r="F132" s="4">
         <v>47</v>
@@ -18098,59 +18090,59 @@
         <v>52</v>
       </c>
       <c r="O132" s="5">
-        <v>26953.34</v>
+        <v>36200.630000000005</v>
       </c>
       <c r="P132" s="5">
-        <v>31445.563333333335</v>
+        <v>36200.630000000005</v>
       </c>
       <c r="Q132" s="6">
-        <v>-0.12277637535478647</v>
+        <v>-0.035179874522262455</v>
       </c>
       <c r="R132" s="7">
-        <v>327.83333333333337</v>
+        <v>369</v>
       </c>
       <c r="S132" s="6">
-        <v>-0.23641304347826086</v>
+        <v>-0.21153846153846156</v>
       </c>
       <c r="T132" s="6">
-        <v>0.34691363296719446</v>
+        <v>0.33898478286151379</v>
       </c>
       <c r="U132" s="6">
-        <v>0.017964790263470129</v>
+        <v>0.012282181276955679</v>
       </c>
       <c r="V132" s="6">
-        <v>0.028759144506766136</v>
+        <v>0.024404368100776147</v>
       </c>
       <c r="W132" s="6">
-        <v>0.0092309524533879667</v>
+        <v>0.0088270148889674025</v>
       </c>
       <c r="X132" s="8">
-        <v>28.846769767441859</v>
+        <v>28.396924404761904</v>
       </c>
       <c r="Y132" s="6">
-        <v>0.70542635658914732</v>
+        <v>0.73809523809523814</v>
       </c>
       <c r="Z132" s="6">
-        <v>0.023255813953488372</v>
+        <v>0.017857142857142856</v>
       </c>
       <c r="AA132" s="8">
-        <v>8.9785988636363641</v>
+        <v>8.6889213872832372</v>
       </c>
       <c r="AB132" s="8">
-        <v>5.8777772357723572</v>
+        <v>6.0139913580246915</v>
       </c>
       <c r="AC132" s="8">
-        <v>15.777647</v>
+        <v>15.618356</v>
       </c>
       <c r="AD132" s="8">
-        <v>23.308139534883722</v>
+        <v>23.243254166666667</v>
       </c>
       <c r="AE132" s="6">
-        <v>0.55813953488372092</v>
+        <v>0.6071428571428571</v>
       </c>
       <c r="AF132" s="9"/>
       <c r="AG132" s="5">
-        <v>-949.83000000000004</v>
+        <v>-1678.03</v>
       </c>
       <c r="AH132" s="10">
         <v>2</v>
@@ -18181,7 +18173,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR132" s="4">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c t="s" r="AS132" s="4">
         <v>56</v>
@@ -18235,7 +18227,7 @@
         <v>84308.150000000009</v>
       </c>
       <c r="Q133" s="6">
-        <v>0.12851468894957652</v>
+        <v>-0.0011120588241912976</v>
       </c>
       <c r="R133" s="7">
         <v>846</v>
@@ -18366,7 +18358,7 @@
         <v>48908.960000000006</v>
       </c>
       <c r="Q134" s="6">
-        <v>-0.015809561640588332</v>
+        <v>-0.059991535707819454</v>
       </c>
       <c r="R134" s="7">
         <v>527</v>
@@ -18443,7 +18435,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR134" s="4">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c t="s" r="AS134" s="4">
         <v>56</v>
@@ -18460,10 +18452,10 @@
         <v>44</v>
       </c>
       <c t="s" r="D135" s="4">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c t="s" r="E135" s="4">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c t="s" r="F135" s="4">
         <v>47</v>
@@ -18497,7 +18489,7 @@
         <v>33272.940000000002</v>
       </c>
       <c r="Q135" s="6">
-        <v>-0.31123404898355456</v>
+        <v>0.061539948755791718</v>
       </c>
       <c r="R135" s="7">
         <v>296</v>
@@ -18533,7 +18525,7 @@
         <v>15.191024615384615</v>
       </c>
       <c r="AC135" s="8">
-        <v>20.405598000000001</v>
+        <v>19.135221999999999</v>
       </c>
       <c r="AD135" s="8">
         <v>25.379258518518519</v>
@@ -18574,7 +18566,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR135" s="4">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c t="s" r="AS135" s="4">
         <v>56</v>
@@ -18594,7 +18586,7 @@
         <v>75</v>
       </c>
       <c t="s" r="E136" s="4">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c t="s" r="F136" s="4">
         <v>47</v>
@@ -18628,7 +18620,7 @@
         <v>77719.610000000001</v>
       </c>
       <c r="Q136" s="6">
-        <v>0.02821969190827267</v>
+        <v>-0.027406939008272957</v>
       </c>
       <c r="R136" s="7">
         <v>683</v>
@@ -18705,7 +18697,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR136" s="4">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c t="s" r="AS136" s="4">
         <v>56</v>
@@ -18725,7 +18717,7 @@
         <v>68</v>
       </c>
       <c t="s" r="E137" s="4">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c t="s" r="F137" s="4">
         <v>47</v>
@@ -18759,7 +18751,7 @@
         <v>39704.919999999998</v>
       </c>
       <c r="Q137" s="6">
-        <v>0.10916644597827507</v>
+        <v>0.0078043122080235783</v>
       </c>
       <c r="R137" s="7">
         <v>424</v>
@@ -18795,7 +18787,7 @@
         <v>4.9048012345679011</v>
       </c>
       <c r="AC137" s="8">
-        <v>8.5449640000000002</v>
+        <v>8.3700060000000001</v>
       </c>
       <c r="AD137" s="8">
         <v>15.0545332</v>
@@ -18856,7 +18848,7 @@
         <v>89</v>
       </c>
       <c t="s" r="E138" s="4">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c t="s" r="F138" s="4">
         <v>47</v>
@@ -18890,7 +18882,7 @@
         <v>26658.870000000003</v>
       </c>
       <c r="Q138" s="6">
-        <v>-0.23521230643180435</v>
+        <v>-0.3028501718105221</v>
       </c>
       <c r="R138" s="7">
         <v>304</v>
@@ -18967,7 +18959,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR138" s="4">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c t="s" r="AS138" s="4">
         <v>56</v>
@@ -19021,7 +19013,7 @@
         <v>24056.82</v>
       </c>
       <c r="Q139" s="6">
-        <v>-0.051218493509689766</v>
+        <v>-0.22000766477813971</v>
       </c>
       <c r="R139" s="7">
         <v>278</v>
@@ -19098,7 +19090,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR139" s="4">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c t="s" r="AS139" s="4">
         <v>56</v>
@@ -19152,7 +19144,7 @@
         <v>29432.079999999998</v>
       </c>
       <c r="Q140" s="6">
-        <v>-0.080996487862392108</v>
+        <v>-0.18889411889205743</v>
       </c>
       <c r="R140" s="7">
         <v>323</v>
@@ -19229,7 +19221,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR140" s="4">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c t="s" r="AS140" s="4">
         <v>56</v>
@@ -19249,7 +19241,7 @@
         <v>86</v>
       </c>
       <c t="s" r="E141" s="4">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c t="s" r="F141" s="4">
         <v>47</v>
@@ -19283,7 +19275,7 @@
         <v>27321.18</v>
       </c>
       <c r="Q141" s="6">
-        <v>-0.025541689107010934</v>
+        <v>-0.06037710541927821</v>
       </c>
       <c r="R141" s="7">
         <v>373</v>
@@ -19360,7 +19352,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR141" s="4">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c t="s" r="AS141" s="4">
         <v>56</v>
@@ -19378,7 +19370,7 @@
       </c>
       <c r="D142" s="4"/>
       <c t="s" r="E142" s="4">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c t="s" r="F142" s="4">
         <v>47</v>
@@ -19412,7 +19404,7 @@
         <v>23952.719999999998</v>
       </c>
       <c r="Q142" s="6">
-        <v>-0.0011317830879746804</v>
+        <v>-0.088976190177349923</v>
       </c>
       <c r="R142" s="7">
         <v>243.99999999999997</v>
@@ -19461,7 +19453,7 @@
         <v>0</v>
       </c>
       <c r="AH142" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI142" s="11"/>
       <c r="AJ142" s="12">
@@ -19509,7 +19501,7 @@
         <v>80</v>
       </c>
       <c t="s" r="E143" s="4">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c t="s" r="F143" s="4">
         <v>47</v>
@@ -19543,7 +19535,7 @@
         <v>20676.619999999999</v>
       </c>
       <c r="Q143" s="6">
-        <v>0.00037544402545663935</v>
+        <v>-0.086916931186089119</v>
       </c>
       <c r="R143" s="7">
         <v>287</v>
@@ -19620,7 +19612,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR143" s="4">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c t="s" r="AS143" s="4">
         <v>56</v>
@@ -19640,7 +19632,7 @@
         <v>136</v>
       </c>
       <c t="s" r="E144" s="4">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c t="s" r="F144" s="4">
         <v>47</v>
@@ -19674,7 +19666,7 @@
         <v>32615.970000000001</v>
       </c>
       <c r="Q144" s="6">
-        <v>0.6340486227105715</v>
+        <v>0.54548319138592283</v>
       </c>
       <c r="R144" s="7">
         <v>408</v>
@@ -19710,7 +19702,7 @@
         <v>2.6137290983606558</v>
       </c>
       <c r="AC144" s="8">
-        <v>5.5440060000000004</v>
+        <v>6.4083540000000001</v>
       </c>
       <c r="AD144" s="8">
         <v>13.335850612244897</v>
@@ -19769,7 +19761,7 @@
         <v>136</v>
       </c>
       <c t="s" r="E145" s="4">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c t="s" r="F145" s="4">
         <v>47</v>
@@ -19803,7 +19795,7 @@
         <v>46359.029999999992</v>
       </c>
       <c r="Q145" s="6">
-        <v>1.0771393840767538</v>
+        <v>1.0117649049902884</v>
       </c>
       <c r="R145" s="7">
         <v>574</v>
@@ -19839,7 +19831,7 @@
         <v>2.0524834437086095</v>
       </c>
       <c r="AC145" s="8">
-        <v>5.6940569999999999</v>
+        <v>7.5546139999999999</v>
       </c>
       <c r="AD145" s="8">
         <v>14.451820860927151</v>
@@ -19898,7 +19890,7 @@
         <v>45</v>
       </c>
       <c t="s" r="E146" s="4">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c t="s" r="F146" s="4">
         <v>47</v>
@@ -19932,7 +19924,7 @@
         <v>16463</v>
       </c>
       <c r="Q146" s="6">
-        <v>-0.27517472326494108</v>
+        <v>-0.34421175152783567</v>
       </c>
       <c r="R146" s="7">
         <v>191</v>
@@ -20009,7 +20001,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR146" s="4">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c t="s" r="AS146" s="4">
         <v>56</v>
@@ -20020,7 +20012,7 @@
         <v>19910</v>
       </c>
       <c r="B147" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C147" s="4">
         <v>44</v>
@@ -20029,7 +20021,7 @@
         <v>125</v>
       </c>
       <c t="s" r="E147" s="4">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c t="s" r="F147" s="4">
         <v>47</v>
@@ -20057,55 +20049,55 @@
         <v>52</v>
       </c>
       <c r="O147" s="5">
-        <v>24538.530000000002</v>
+        <v>32053.990000000002</v>
       </c>
       <c r="P147" s="5">
-        <v>28628.285000000003</v>
+        <v>32053.990000000002</v>
       </c>
       <c r="Q147" s="6">
-        <v>0.18698201177102303</v>
+        <v>0.22991525960260106</v>
       </c>
       <c r="R147" s="7">
-        <v>297.5</v>
+        <v>338</v>
       </c>
       <c r="S147" s="6">
-        <v>0.23786407766990281</v>
+        <v>0.21582733812949639</v>
       </c>
       <c r="T147" s="6">
-        <v>0.42788151939011837</v>
+        <v>0.33018421419611099</v>
       </c>
       <c r="U147" s="6">
-        <v>0.1252635549073233</v>
+        <v>0.02656335451530371</v>
       </c>
       <c r="V147" s="6">
-        <v>0.081105102872910492</v>
+        <v>0.076159114668719871</v>
       </c>
       <c r="W147" s="6">
-        <v>0.0523217975974926</v>
+        <v>0.050117114905195888</v>
       </c>
       <c r="X147" s="8">
-        <v>18.541162416107383</v>
+        <v>18.72316153846154</v>
       </c>
       <c r="Y147" s="6">
-        <v>0.82550335570469802</v>
+        <v>0.84615384615384615</v>
       </c>
       <c r="Z147" s="6">
-        <v>0.040268456375838924</v>
+        <v>0.030769230769230771</v>
       </c>
       <c r="AA147" s="8">
-        <v>4.4687250996015937</v>
+        <v>4.7780780780780781</v>
       </c>
       <c r="AB147" s="8">
-        <v>3.1062500000000002</v>
+        <v>2.7982090909090909</v>
       </c>
       <c r="AC147" s="8">
-        <v>7.5856680000000001</v>
+        <v>7.5889579999999999</v>
       </c>
       <c r="AD147" s="8">
-        <v>13.221140939597316</v>
+        <v>13.528803589743591</v>
       </c>
       <c r="AE147" s="6">
-        <v>0.93959731543624159</v>
+        <v>0.9538461538461539</v>
       </c>
       <c r="AF147" s="9"/>
       <c r="AG147" s="5">
@@ -20140,7 +20132,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR147" s="4">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c t="s" r="AS147" s="4">
         <v>56</v>
@@ -20160,7 +20152,7 @@
         <v>86</v>
       </c>
       <c t="s" r="E148" s="4">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c t="s" r="F148" s="4">
         <v>47</v>
@@ -20194,7 +20186,7 @@
         <v>33115.379999999997</v>
       </c>
       <c r="Q148" s="6">
-        <v>0.22850666646881179</v>
+        <v>0.11451750511144176</v>
       </c>
       <c r="R148" s="7">
         <v>455</v>
@@ -20230,7 +20222,7 @@
         <v>6.9058304182509511</v>
       </c>
       <c r="AC148" s="8">
-        <v>10.843400000000001</v>
+        <v>11.962999</v>
       </c>
       <c r="AD148" s="8">
         <v>17.50060606060606</v>
@@ -20271,7 +20263,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR148" s="4">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c t="s" r="AS148" s="4">
         <v>56</v>
@@ -20282,7 +20274,7 @@
         <v>19912</v>
       </c>
       <c r="B149" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C149" s="4">
         <v>44</v>
@@ -20291,7 +20283,7 @@
         <v>80</v>
       </c>
       <c t="s" r="E149" s="4">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c t="s" r="F149" s="4">
         <v>47</v>
@@ -20319,59 +20311,59 @@
         <v>52</v>
       </c>
       <c r="O149" s="5">
-        <v>28094.530000000002</v>
+        <v>34499.090000000004</v>
       </c>
       <c r="P149" s="5">
-        <v>32776.951666666668</v>
+        <v>34499.090000000004</v>
       </c>
       <c r="Q149" s="6">
-        <v>0.84458628107213585</v>
+        <v>0.78514143608843989</v>
       </c>
       <c r="R149" s="7">
-        <v>360.5</v>
+        <v>387</v>
       </c>
       <c r="S149" s="6">
-        <v>0.62631578947368416</v>
+        <v>0.61924686192468603</v>
       </c>
       <c r="T149" s="6">
-        <v>-3.6711456073477651</v>
+        <v>0.30216759340608695</v>
       </c>
       <c r="U149" s="6">
-        <v>-6.3640395621496433</v>
+        <v>-2.37674451702929</v>
       </c>
       <c r="V149" s="6">
-        <v>0.013411489709918621</v>
+        <v>0.019797391757289833</v>
       </c>
       <c r="W149" s="6">
-        <v>-0.018767372153938863</v>
+        <v>-0.012198814519455443</v>
       </c>
       <c r="X149" s="8">
-        <v>22.5752688172043</v>
+        <v>22.049789029535866</v>
       </c>
       <c r="Y149" s="6">
-        <v>0.83870967741935487</v>
+        <v>0.78059071729957807</v>
       </c>
       <c r="Z149" s="6">
-        <v>0.016129032258064516</v>
+        <v>0.012658227848101266</v>
       </c>
       <c r="AA149" s="8">
-        <v>6.483276369863014</v>
+        <v>6.1212081743869211</v>
       </c>
       <c r="AB149" s="8">
-        <v>1.9391348066298344</v>
+        <v>1.8009380952380953</v>
       </c>
       <c r="AC149" s="8">
-        <v>8.3440349999999999</v>
+        <v>7.8479950000000001</v>
       </c>
       <c r="AD149" s="8">
-        <v>16.105017741935484</v>
+        <v>15.638466666666668</v>
       </c>
       <c r="AE149" s="6">
-        <v>0.95161290322580649</v>
+        <v>0.95780590717299574</v>
       </c>
       <c r="AF149" s="9"/>
       <c r="AG149" s="5">
-        <v>-163</v>
+        <v>-200.90000000000001</v>
       </c>
       <c r="AH149" s="10">
         <v>4</v>
@@ -20402,7 +20394,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR149" s="4">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c t="s" r="AS149" s="4">
         <v>56</v>
@@ -20422,7 +20414,7 @@
         <v>103</v>
       </c>
       <c t="s" r="E150" s="4">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c t="s" r="F150" s="4">
         <v>47</v>
@@ -20456,7 +20448,7 @@
         <v>54534.940000000002</v>
       </c>
       <c r="Q150" s="6">
-        <v>0.60988705243186625</v>
+        <v>0.43092421249228252</v>
       </c>
       <c r="R150" s="7">
         <v>618</v>
@@ -20533,7 +20525,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR150" s="4">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c t="s" r="AS150" s="4">
         <v>56</v>
@@ -20553,7 +20545,7 @@
         <v>136</v>
       </c>
       <c t="s" r="E151" s="4">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c t="s" r="F151" s="4">
         <v>47</v>
@@ -20626,7 +20618,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR151" s="4">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c t="s" r="AS151" s="4">
         <v>56</v>
@@ -20646,7 +20638,7 @@
         <v>70</v>
       </c>
       <c t="s" r="E152" s="4">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c t="s" r="F152" s="4">
         <v>47</v>
@@ -20680,7 +20672,7 @@
         <v>15258.84</v>
       </c>
       <c r="Q152" s="6">
-        <v>-0.043140343605202025</v>
+        <v>-0.12448517995320307</v>
       </c>
       <c r="R152" s="7">
         <v>194</v>
@@ -20757,7 +20749,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR152" s="4">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c t="s" r="AS152" s="4">
         <v>56</v>
@@ -20768,7 +20760,7 @@
         <v>19927</v>
       </c>
       <c r="B153" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C153" s="4">
         <v>44</v>
@@ -20777,7 +20769,7 @@
         <v>70</v>
       </c>
       <c t="s" r="E153" s="4">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c t="s" r="F153" s="4">
         <v>47</v>
@@ -20805,59 +20797,59 @@
         <v>52</v>
       </c>
       <c r="O153" s="5">
-        <v>9084.4200000000001</v>
+        <v>11172.07</v>
       </c>
       <c r="P153" s="5">
-        <v>10598.49</v>
+        <v>11172.069999999998</v>
       </c>
       <c r="Q153" s="6">
-        <v>-0.16984104107365805</v>
+        <v>-0.18936472336482635</v>
       </c>
       <c r="R153" s="7">
-        <v>138.83333333333331</v>
+        <v>144</v>
       </c>
       <c r="S153" s="6">
-        <v>-0.0703125</v>
+        <v>-0.1910112359550562</v>
       </c>
       <c r="T153" s="6">
         <v>0</v>
       </c>
       <c r="U153" s="6">
-        <v>-0.32787343605865865</v>
+        <v>-0.33052782519264556</v>
       </c>
       <c r="V153" s="6">
-        <v>0.15359032277239493</v>
+        <v>0.15561086709983021</v>
       </c>
       <c r="W153" s="6">
-        <v>0.066484046312257697</v>
+        <v>0.073876685341212514</v>
       </c>
       <c r="X153" s="8">
-        <v>35.499360256410256</v>
+        <v>35.683517582417579</v>
       </c>
       <c r="Y153" s="6">
-        <v>0.61538461538461542</v>
+        <v>0.65217391304347827</v>
       </c>
       <c r="Z153" s="6">
-        <v>0.34615384615384615</v>
+        <v>0.32967032967032966</v>
       </c>
       <c r="AA153" s="8">
-        <v>8.7831924369747902</v>
+        <v>8.7278534246575337</v>
       </c>
       <c r="AB153" s="8">
-        <v>10.356061038961039</v>
+        <v>10.430403296703297</v>
       </c>
       <c r="AC153" s="8">
-        <v>18.300504</v>
+        <v>18.500260000000001</v>
       </c>
       <c r="AD153" s="8">
-        <v>25.100215384615385</v>
+        <v>25.339675000000003</v>
       </c>
       <c r="AE153" s="6">
-        <v>0.42307692307692307</v>
+        <v>0.39560439560439559</v>
       </c>
       <c r="AF153" s="9"/>
       <c r="AG153" s="5">
-        <v>-986.29999999999995</v>
+        <v>-1425.3</v>
       </c>
       <c r="AH153" s="10">
         <v>1</v>
@@ -20890,7 +20882,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR153" s="4">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c t="s" r="AS153" s="4">
         <v>56</v>
@@ -20910,7 +20902,7 @@
         <v>89</v>
       </c>
       <c t="s" r="E154" s="4">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c t="s" r="F154" s="4">
         <v>47</v>
@@ -20944,7 +20936,7 @@
         <v>24471.48</v>
       </c>
       <c r="Q154" s="6">
-        <v>0.046327215945968891</v>
+        <v>-0.050719985538611234</v>
       </c>
       <c r="R154" s="7">
         <v>290</v>
@@ -20980,7 +20972,7 @@
         <v>8.3632984455958557</v>
       </c>
       <c r="AC154" s="8">
-        <v>10.485870999999999</v>
+        <v>12.292273</v>
       </c>
       <c r="AD154" s="8">
         <v>18.754083000000001</v>
@@ -21021,7 +21013,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR154" s="4">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c t="s" r="AS154" s="4">
         <v>56</v>
@@ -21032,7 +21024,7 @@
         <v>19930</v>
       </c>
       <c r="B155" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C155" s="4">
         <v>44</v>
@@ -21041,7 +21033,7 @@
         <v>89</v>
       </c>
       <c t="s" r="E155" s="4">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c t="s" r="F155" s="4">
         <v>47</v>
@@ -21069,55 +21061,55 @@
         <v>52</v>
       </c>
       <c r="O155" s="5">
-        <v>27829.470000000001</v>
+        <v>35503.389999999999</v>
       </c>
       <c r="P155" s="5">
-        <v>32467.715</v>
+        <v>35503.389999999999</v>
       </c>
       <c r="Q155" s="6">
-        <v>0.23851716136454737</v>
+        <v>0.23015746244479995</v>
       </c>
       <c r="R155" s="7">
-        <v>431.66666666666663</v>
+        <v>479</v>
       </c>
       <c r="S155" s="6">
-        <v>0.03064066852367664</v>
+        <v>0.050438596491228171</v>
       </c>
       <c r="T155" s="6">
-        <v>0.34679516354425721</v>
+        <v>0.34337135974902677</v>
       </c>
       <c r="U155" s="6">
-        <v>0.037508281688440351</v>
+        <v>0.029030391182363151</v>
       </c>
       <c r="V155" s="6">
-        <v>0.067540740085959242</v>
+        <v>0.065325606934999725</v>
       </c>
       <c r="W155" s="6">
-        <v>0.035274584819617476</v>
+        <v>0.034997517138504242</v>
       </c>
       <c r="X155" s="8">
-        <v>28.771503785488957</v>
+        <v>28.985436893203882</v>
       </c>
       <c r="Y155" s="6">
-        <v>0.17665615141955837</v>
+        <v>0.17233009708737865</v>
       </c>
       <c r="Z155" s="6">
-        <v>0.16088328075709779</v>
+        <v>0.15776699029126215</v>
       </c>
       <c r="AA155" s="8">
-        <v>4.6321299465240644</v>
+        <v>5.2663573195876294</v>
       </c>
       <c r="AB155" s="8">
-        <v>13.831449657534247</v>
+        <v>12.972294764397905</v>
       </c>
       <c r="AC155" s="8">
-        <v>18.398115000000001</v>
+        <v>18.210377000000001</v>
       </c>
       <c r="AD155" s="8">
-        <v>23.916771293375394</v>
+        <v>23.886690533980584</v>
       </c>
       <c r="AE155" s="6">
-        <v>0.67823343848580442</v>
+        <v>0.64805825242718451</v>
       </c>
       <c r="AF155" s="9"/>
       <c r="AG155" s="5">
@@ -21152,7 +21144,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR155" s="4">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c t="s" r="AS155" s="4">
         <v>56</v>
@@ -21163,7 +21155,7 @@
         <v>19931</v>
       </c>
       <c r="B156" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C156" s="4">
         <v>44</v>
@@ -21200,55 +21192,55 @@
         <v>52</v>
       </c>
       <c r="O156" s="5">
-        <v>22604.239999999998</v>
+        <v>30210.189999999999</v>
       </c>
       <c r="P156" s="5">
-        <v>26371.613333333331</v>
+        <v>30210.189999999999</v>
       </c>
       <c r="Q156" s="6">
-        <v>-0.16144373786454602</v>
+        <v>-0.13037674801522203</v>
       </c>
       <c r="R156" s="7">
-        <v>310.33333333333337</v>
+        <v>352</v>
       </c>
       <c r="S156" s="6">
-        <v>-0.16614420062695912</v>
+        <v>-0.19266055045871555</v>
       </c>
       <c r="T156" s="6">
-        <v>0.17714286346278396</v>
+        <v>0.29169070105153261</v>
       </c>
       <c r="U156" s="6">
-        <v>-0.32422148234136605</v>
+        <v>-0.20794733498862469</v>
       </c>
       <c r="V156" s="6">
-        <v>0.089674680502419016</v>
+        <v>0.0815168656668495</v>
       </c>
       <c r="W156" s="6">
-        <v>0.059646243359652878</v>
+        <v>0.054925506923326206</v>
       </c>
       <c r="X156" s="8">
-        <v>24.142176530612247</v>
+        <v>24.751009848484848</v>
       </c>
       <c r="Y156" s="6">
-        <v>0.79591836734693877</v>
+        <v>0.74242424242424243</v>
       </c>
       <c r="Z156" s="6">
-        <v>0.020408163265306121</v>
+        <v>0.030303030303030304</v>
       </c>
       <c r="AA156" s="8">
-        <v>4.1655973584905661</v>
+        <v>4.2659544159544156</v>
       </c>
       <c r="AB156" s="8">
-        <v>3.914717021276596</v>
+        <v>4.8950672000000006</v>
       </c>
       <c r="AC156" s="8">
-        <v>8.2990390000000005</v>
+        <v>9.2764520000000008</v>
       </c>
       <c r="AD156" s="8">
-        <v>14.92125918367347</v>
+        <v>15.776641666666668</v>
       </c>
       <c r="AE156" s="6">
-        <v>0.80612244897959184</v>
+        <v>0.78787878787878785</v>
       </c>
       <c r="AF156" s="9"/>
       <c r="AG156" s="5">
@@ -21283,7 +21275,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR156" s="4">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c t="s" r="AS156" s="4">
         <v>56</v>
@@ -21303,7 +21295,7 @@
         <v>68</v>
       </c>
       <c t="s" r="E157" s="4">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c t="s" r="F157" s="4">
         <v>47</v>
@@ -21337,7 +21329,7 @@
         <v>19912.860000000004</v>
       </c>
       <c r="Q157" s="6">
-        <v>0.29906410361793823</v>
+        <v>0.19168893905245921</v>
       </c>
       <c r="R157" s="7">
         <v>242</v>
@@ -21373,7 +21365,7 @@
         <v>6.6309754716981137</v>
       </c>
       <c r="AC157" s="8">
-        <v>10.075070999999999</v>
+        <v>10.552820000000001</v>
       </c>
       <c r="AD157" s="8">
         <v>14.224657534246576</v>
@@ -21414,7 +21406,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR157" s="4">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c t="s" r="AS157" s="4">
         <v>56</v>
@@ -21468,7 +21460,7 @@
         <v>17707.34</v>
       </c>
       <c r="Q158" s="6">
-        <v>-0.38723902271570365</v>
+        <v>-0.4476977607657413</v>
       </c>
       <c r="R158" s="7">
         <v>173</v>
@@ -21504,7 +21496,7 @@
         <v>10.386569902912623</v>
       </c>
       <c r="AC158" s="8">
-        <v>13.553557</v>
+        <v>14.637862999999999</v>
       </c>
       <c r="AD158" s="8">
         <v>21.593527184466019</v>
@@ -21563,7 +21555,7 @@
       </c>
       <c r="D159" s="4"/>
       <c t="s" r="E159" s="4">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c t="s" r="F159" s="4">
         <v>47</v>
@@ -21597,7 +21589,7 @@
         <v>34487.660000000003</v>
       </c>
       <c r="Q159" s="6">
-        <v>0.036480954985604219</v>
+        <v>-0.068495230069469226</v>
       </c>
       <c r="R159" s="7">
         <v>407</v>
@@ -21676,7 +21668,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR159" s="4">
-        <v>158</v>
+        <v>131</v>
       </c>
       <c t="s" r="AS159" s="4">
         <v>56</v>
@@ -21687,7 +21679,7 @@
         <v>19943</v>
       </c>
       <c r="B160" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C160" s="4">
         <v>44</v>
@@ -21696,7 +21688,7 @@
         <v>80</v>
       </c>
       <c t="s" r="E160" s="4">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c t="s" r="F160" s="4">
         <v>47</v>
@@ -21724,55 +21716,55 @@
         <v>52</v>
       </c>
       <c r="O160" s="5">
-        <v>17711.700000000001</v>
+        <v>21234.48</v>
       </c>
       <c r="P160" s="5">
-        <v>20663.650000000001</v>
+        <v>21234.48</v>
       </c>
       <c r="Q160" s="6">
-        <v>0.36388958010049799</v>
+        <v>0.28897397950945591</v>
       </c>
       <c r="R160" s="7">
-        <v>249.66666666666666</v>
+        <v>256</v>
       </c>
       <c r="S160" s="6">
-        <v>0.32098765432098753</v>
+        <v>0.16363636363636358</v>
       </c>
       <c r="T160" s="6">
-        <v>0.35114750701513686</v>
+        <v>0.35696408388620776</v>
       </c>
       <c r="U160" s="6">
-        <v>0.010980272926935302</v>
+        <v>0.011902184560205855</v>
       </c>
       <c r="V160" s="6">
-        <v>0.041755534477209977</v>
+        <v>0.050373590499979276</v>
       </c>
       <c r="W160" s="6">
-        <v>0.0077136299734074081</v>
+        <v>0.012670289077010599</v>
       </c>
       <c r="X160" s="8">
-        <v>25.858550434782607</v>
+        <v>25.452592592592591</v>
       </c>
       <c r="Y160" s="6">
-        <v>0.65517241379310343</v>
+        <v>0.66176470588235292</v>
       </c>
       <c r="Z160" s="6">
-        <v>0.060869565217391307</v>
+        <v>0.059259259259259262</v>
       </c>
       <c r="AA160" s="8">
-        <v>7.687581372549019</v>
+        <v>7.4293195918367347</v>
       </c>
       <c r="AB160" s="8">
-        <v>7.6155954128440371</v>
+        <v>7.6266921874999998</v>
       </c>
       <c r="AC160" s="8">
-        <v>13.669762</v>
+        <v>13.368603</v>
       </c>
       <c r="AD160" s="8">
-        <v>20.075797391304349</v>
+        <v>19.782962962962962</v>
       </c>
       <c r="AE160" s="6">
-        <v>0.77391304347826084</v>
+        <v>0.77777777777777779</v>
       </c>
       <c r="AF160" s="9"/>
       <c r="AG160" s="5">
@@ -21807,13 +21799,13 @@
         <v>55</v>
       </c>
       <c t="s" r="AR160" s="4">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c t="s" r="AS160" s="4">
         <v>56</v>
       </c>
     </row>
-    <row r="161" ht="24.75" customHeight="1">
+    <row r="161" ht="13.5" customHeight="1">
       <c r="A161" s="2">
         <v>19944</v>
       </c>
@@ -21827,7 +21819,7 @@
         <v>94</v>
       </c>
       <c t="s" r="E161" s="4">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c t="s" r="F161" s="4">
         <v>47</v>
@@ -21861,7 +21853,7 @@
         <v>47777.549999999996</v>
       </c>
       <c r="Q161" s="6">
-        <v>0.14057972017838627</v>
+        <v>0.027710677510738968</v>
       </c>
       <c r="R161" s="7">
         <v>519</v>
@@ -21897,7 +21889,7 @@
         <v>13.814272375690608</v>
       </c>
       <c r="AC161" s="8">
-        <v>26.171211</v>
+        <v>24.827117000000001</v>
       </c>
       <c r="AD161" s="8">
         <v>31.754143646408838</v>
@@ -21938,7 +21930,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR161" s="4">
-        <v>258</v>
+        <v>219</v>
       </c>
       <c t="s" r="AS161" s="4">
         <v>56</v>
@@ -21955,10 +21947,10 @@
         <v>44</v>
       </c>
       <c t="s" r="D162" s="4">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c t="s" r="E162" s="4">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c t="s" r="F162" s="4">
         <v>47</v>
@@ -21992,7 +21984,7 @@
         <v>25011.829999999998</v>
       </c>
       <c r="Q162" s="6">
-        <v>0.068826355560246855</v>
+        <v>-0.026644863446436906</v>
       </c>
       <c r="R162" s="7">
         <v>315</v>
@@ -22028,7 +22020,7 @@
         <v>8.3820773584905659</v>
       </c>
       <c r="AC162" s="8">
-        <v>12.631722999999999</v>
+        <v>17.426615000000002</v>
       </c>
       <c r="AD162" s="8">
         <v>23.494442105263158</v>
@@ -22069,7 +22061,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR162" s="4">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c t="s" r="AS162" s="4">
         <v>56</v>
@@ -22089,7 +22081,7 @@
         <v>68</v>
       </c>
       <c t="s" r="E163" s="4">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c t="s" r="F163" s="4">
         <v>47</v>
@@ -22123,7 +22115,7 @@
         <v>67038.169999999998</v>
       </c>
       <c r="Q163" s="6">
-        <v>0.25829051012084348</v>
+        <v>0.11700850159316345</v>
       </c>
       <c r="R163" s="7">
         <v>680</v>
@@ -22159,7 +22151,7 @@
         <v>6.1876066666666665</v>
       </c>
       <c r="AC163" s="8">
-        <v>9.7323389999999996</v>
+        <v>9.735061</v>
       </c>
       <c r="AD163" s="8">
         <v>16.568020050761422</v>
@@ -22200,7 +22192,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR163" s="4">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c t="s" r="AS163" s="4">
         <v>56</v>
@@ -22220,7 +22212,7 @@
         <v>89</v>
       </c>
       <c t="s" r="E164" s="4">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c t="s" r="F164" s="4">
         <v>47</v>
@@ -22254,7 +22246,7 @@
         <v>13830.549999999999</v>
       </c>
       <c r="Q164" s="6">
-        <v>0.35370929001113827</v>
+        <v>0.2423836288555703</v>
       </c>
       <c r="R164" s="7">
         <v>203</v>
@@ -22331,7 +22323,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR164" s="4">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c t="s" r="AS164" s="4">
         <v>56</v>
@@ -22342,7 +22334,7 @@
         <v>19951</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22351,7 +22343,7 @@
         <v>80</v>
       </c>
       <c t="s" r="E165" s="4">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c t="s" r="F165" s="4">
         <v>47</v>
@@ -22379,59 +22371,59 @@
         <v>52</v>
       </c>
       <c r="O165" s="5">
-        <v>26164.830000000002</v>
+        <v>32665.860000000001</v>
       </c>
       <c r="P165" s="5">
-        <v>30525.634999999998</v>
+        <v>32665.860000000004</v>
       </c>
       <c r="Q165" s="6">
-        <v>-0.20109452353509549</v>
+        <v>-0.23325355061273545</v>
       </c>
       <c r="R165" s="7">
-        <v>326.66666666666663</v>
+        <v>354</v>
       </c>
       <c r="S165" s="6">
-        <v>-0.2452830188679247</v>
+        <v>-0.31128404669260701</v>
       </c>
       <c r="T165" s="6">
-        <v>0.34210372091085628</v>
+        <v>0.33329549260298064</v>
       </c>
       <c r="U165" s="6">
-        <v>-0.023470601567065406</v>
+        <v>-0.028689466617440963</v>
       </c>
       <c r="V165" s="6">
-        <v>0.027493490307408833</v>
+        <v>0.026653729612506758</v>
       </c>
       <c r="W165" s="6">
-        <v>-0.0036999093821744686</v>
+        <v>-0.0022287183010029428</v>
       </c>
       <c r="X165" s="8">
-        <v>23.008163945578232</v>
+        <v>23.933070526315792</v>
       </c>
       <c r="Y165" s="6">
-        <v>0.61224489795918369</v>
+        <v>0.58421052631578951</v>
       </c>
       <c r="Z165" s="6">
-        <v>0.027210884353741496</v>
+        <v>0.068421052631578952</v>
       </c>
       <c r="AA165" s="8">
-        <v>4.2864620938628155</v>
+        <v>4.8198005698005701</v>
       </c>
       <c r="AB165" s="8">
-        <v>4.654745138888889</v>
+        <v>4.7959239130434783</v>
       </c>
       <c r="AC165" s="8">
-        <v>9.218451</v>
+        <v>9.8189670000000007</v>
       </c>
       <c r="AD165" s="8">
-        <v>15.958502721088434</v>
+        <v>16.466315263157895</v>
       </c>
       <c r="AE165" s="6">
-        <v>0.77551020408163263</v>
+        <v>0.74210526315789471</v>
       </c>
       <c r="AF165" s="9"/>
       <c r="AG165" s="5">
-        <v>-895.36000000000001</v>
+        <v>-1047.0599999999999</v>
       </c>
       <c r="AH165" s="10">
         <v>1</v>
@@ -22462,7 +22454,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR165" s="4">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c t="s" r="AS165" s="4">
         <v>56</v>
@@ -22473,7 +22465,7 @@
         <v>19954</v>
       </c>
       <c r="B166" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C166" s="4">
         <v>44</v>
@@ -22482,7 +22474,7 @@
         <v>83</v>
       </c>
       <c t="s" r="E166" s="4">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c t="s" r="F166" s="4">
         <v>47</v>
@@ -22510,59 +22502,59 @@
         <v>52</v>
       </c>
       <c r="O166" s="5">
-        <v>10166.59</v>
+        <v>14056.93</v>
       </c>
       <c r="P166" s="5">
-        <v>11861.021666666667</v>
+        <v>14056.930000000002</v>
       </c>
       <c r="Q166" s="6">
-        <v>-0.093269623046193684</v>
+        <v>-0.0042749028141398915</v>
       </c>
       <c r="R166" s="7">
-        <v>150.5</v>
+        <v>180</v>
       </c>
       <c r="S166" s="6">
-        <v>-0.16774193548387084</v>
+        <v>-0.14691943127962082</v>
       </c>
       <c r="T166" s="6">
-        <v>0.3995035306823625</v>
+        <v>0.40261976832779273</v>
       </c>
       <c r="U166" s="6">
-        <v>0.052081238645406182</v>
+        <v>0.049630175294321024</v>
       </c>
       <c r="V166" s="6">
-        <v>0.16090188548962828</v>
+        <v>0.13986126415938616</v>
       </c>
       <c r="W166" s="6">
-        <v>0.089041999333109731</v>
+        <v>0.079441243571676035</v>
       </c>
       <c r="X166" s="8">
-        <v>25.232352941176469</v>
+        <v>26.043860000000002</v>
       </c>
       <c r="Y166" s="6">
-        <v>0.79411764705882348</v>
+        <v>0.78947368421052633</v>
       </c>
       <c r="Z166" s="6">
-        <v>0.044117647058823532</v>
+        <v>0.052631578947368418</v>
       </c>
       <c r="AA166" s="8">
-        <v>5.5646508064516134</v>
+        <v>6.4324712643678161</v>
       </c>
       <c r="AB166" s="8">
-        <v>3.3235294117647061</v>
+        <v>3.4554389473684211</v>
       </c>
       <c r="AC166" s="8">
-        <v>9.400582</v>
+        <v>10.263249999999999</v>
       </c>
       <c r="AD166" s="8">
-        <v>16.369608823529411</v>
+        <v>17.236667368421053</v>
       </c>
       <c r="AE166" s="6">
-        <v>0.80882352941176472</v>
+        <v>0.77894736842105261</v>
       </c>
       <c r="AF166" s="9"/>
       <c r="AG166" s="5">
-        <v>-212.90000000000001</v>
+        <v>-463.69999999999999</v>
       </c>
       <c r="AH166" s="10">
         <v>3</v>
@@ -22593,7 +22585,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR166" s="4">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c t="s" r="AS166" s="4">
         <v>56</v>
@@ -22613,7 +22605,7 @@
         <v>68</v>
       </c>
       <c t="s" r="E167" s="4">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c t="s" r="F167" s="4">
         <v>47</v>
@@ -22647,7 +22639,7 @@
         <v>15236.08</v>
       </c>
       <c r="Q167" s="6">
-        <v>-0.87967409509645289</v>
+        <v>-0.51161839505492179</v>
       </c>
       <c r="R167" s="7">
         <v>180</v>
@@ -22724,7 +22716,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR167" s="4">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c t="s" r="AS167" s="4">
         <v>56</v>
@@ -22741,10 +22733,10 @@
         <v>44</v>
       </c>
       <c t="s" r="D168" s="4">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c t="s" r="E168" s="4">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c t="s" r="F168" s="4">
         <v>47</v>
@@ -22778,7 +22770,7 @@
         <v>29888.889999999996</v>
       </c>
       <c r="Q168" s="6">
-        <v>-0.34528776974477537</v>
+        <v>-0.38070773914084866</v>
       </c>
       <c r="R168" s="7">
         <v>334</v>
@@ -22787,10 +22779,10 @@
         <v>-0.3837638376383764</v>
       </c>
       <c r="T168" s="6">
-        <v>0.40391587308862931</v>
+        <v>0.40466263886012499</v>
       </c>
       <c r="U168" s="6">
-        <v>0.062771387629316444</v>
+        <v>0.063518153400812141</v>
       </c>
       <c r="V168" s="6">
         <v>0.028875980339182889</v>
@@ -22855,7 +22847,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR168" s="4">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c t="s" r="AS168" s="4">
         <v>56</v>
@@ -22866,7 +22858,7 @@
         <v>19959</v>
       </c>
       <c r="B169" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C169" s="4">
         <v>44</v>
@@ -22875,7 +22867,7 @@
         <v>103</v>
       </c>
       <c t="s" r="E169" s="4">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c t="s" r="F169" s="4">
         <v>47</v>
@@ -22903,55 +22895,55 @@
         <v>52</v>
       </c>
       <c r="O169" s="5">
-        <v>13370.799999999999</v>
+        <v>21463.259999999998</v>
       </c>
       <c r="P169" s="5">
-        <v>15599.266666666665</v>
+        <v>21463.259999999998</v>
       </c>
       <c r="Q169" s="6"/>
       <c r="R169" s="7">
-        <v>207.66666666666669</v>
+        <v>278</v>
       </c>
       <c r="S169" s="6"/>
       <c r="T169" s="6">
-        <v>0.59573860950728452</v>
+        <v>1.0077963366236071</v>
       </c>
       <c r="U169" s="6">
-        <v>0.24897252221258265</v>
+        <v>0.66209116415679636</v>
       </c>
       <c r="V169" s="6">
-        <v>0.065696517785024083</v>
+        <v>0.055320626969062488</v>
       </c>
       <c r="W169" s="6">
-        <v>0.013109537200466689</v>
+        <v>0.016007866465765221</v>
       </c>
       <c r="X169" s="8">
-        <v>22.612585714285711</v>
+        <v>23.069375000000001</v>
       </c>
       <c r="Y169" s="6">
-        <v>1</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="Z169" s="6">
-        <v>0.040816326530612242</v>
+        <v>0.025000000000000001</v>
       </c>
       <c r="AA169" s="8">
-        <v>5.1270114942528737</v>
+        <v>5.4958180811808122</v>
       </c>
       <c r="AB169" s="8">
-        <v>3.7564612244897959</v>
+        <v>3.6717092105263154</v>
       </c>
       <c r="AC169" s="8">
-        <v>8.4460040000000003</v>
+        <v>8.7375729999999994</v>
       </c>
       <c r="AD169" s="8">
-        <v>15.303402040816326</v>
+        <v>15.339167499999999</v>
       </c>
       <c r="AE169" s="6">
-        <v>0.91836734693877553</v>
+        <v>0.90000000000000002</v>
       </c>
       <c r="AF169" s="9"/>
       <c r="AG169" s="5">
-        <v>-1774.2</v>
+        <v>-2966.4000000000001</v>
       </c>
       <c r="AH169" s="10">
         <v>3</v>
@@ -22982,7 +22974,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR169" s="4">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c t="s" r="AS169" s="4">
         <v>56</v>
@@ -22993,7 +22985,7 @@
         <v>19961</v>
       </c>
       <c r="B170" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C170" s="4">
         <v>44</v>
@@ -23002,7 +22994,7 @@
         <v>80</v>
       </c>
       <c t="s" r="E170" s="4">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c t="s" r="F170" s="4">
         <v>47</v>
@@ -23030,55 +23022,55 @@
         <v>52</v>
       </c>
       <c r="O170" s="5">
-        <v>15007.6</v>
+        <v>19774.209999999999</v>
       </c>
       <c r="P170" s="5">
-        <v>17508.866666666665</v>
+        <v>19774.209999999999</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="7">
-        <v>180.83333333333331</v>
+        <v>208</v>
       </c>
       <c r="S170" s="6"/>
       <c r="T170" s="6">
-        <v>0.3197528452250859</v>
+        <v>0.33569606067701313</v>
       </c>
       <c r="U170" s="6">
-        <v>-0.033149684160025589</v>
+        <v>-0.018243237024386818</v>
       </c>
       <c r="V170" s="6">
-        <v>0.024985740558117218</v>
+        <v>0.030454895543235355</v>
       </c>
       <c r="W170" s="6">
-        <v>0.0053083770889416028</v>
+        <v>0.012581109434966049</v>
       </c>
       <c r="X170" s="8">
-        <v>24.595238095238095</v>
+        <v>25.225151818181818</v>
       </c>
       <c r="Y170" s="6">
-        <v>0.34523809523809523</v>
+        <v>0.41818181818181815</v>
       </c>
       <c r="Z170" s="6">
-        <v>0.011904761904761904</v>
+        <v>0.018181818181818181</v>
       </c>
       <c r="AA170" s="8">
-        <v>5.8112528662420386</v>
+        <v>6.5477780952380957</v>
       </c>
       <c r="AB170" s="8">
-        <v>5.0861842105263158</v>
+        <v>5.0305558823529415</v>
       </c>
       <c r="AC170" s="8">
-        <v>11.007065000000001</v>
+        <v>11.867826000000001</v>
       </c>
       <c r="AD170" s="8">
-        <v>17.066270238095239</v>
+        <v>18.166060909090909</v>
       </c>
       <c r="AE170" s="6">
-        <v>0.80952380952380953</v>
+        <v>0.78181818181818186</v>
       </c>
       <c r="AF170" s="9"/>
       <c r="AG170" s="5">
-        <v>-519.89999999999998</v>
+        <v>-700.5</v>
       </c>
       <c r="AH170" s="10">
         <v>2</v>
@@ -23109,7 +23101,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR170" s="4">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c t="s" r="AS170" s="4">
         <v>56</v>
@@ -23120,7 +23112,7 @@
         <v>19962</v>
       </c>
       <c r="B171" s="3">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c t="s" r="C171" s="4">
         <v>44</v>
@@ -23129,7 +23121,7 @@
         <v>45</v>
       </c>
       <c t="s" r="E171" s="4">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c t="s" r="F171" s="4">
         <v>47</v>
@@ -23157,55 +23149,55 @@
         <v>52</v>
       </c>
       <c r="O171" s="5">
-        <v>4985.6899999999996</v>
+        <v>20752.619999999999</v>
       </c>
       <c r="P171" s="5">
-        <v>11633.276666666665</v>
+        <v>20752.619999999999</v>
       </c>
       <c r="Q171" s="6"/>
       <c r="R171" s="7">
-        <v>147</v>
+        <v>229.99999999999997</v>
       </c>
       <c r="S171" s="6"/>
       <c r="T171" s="6">
-        <v>0.40666487487188341</v>
+        <v>1.3551449021858446</v>
       </c>
       <c r="U171" s="6">
-        <v>-0.00492308988324585</v>
+        <v>0.99811528375694258</v>
       </c>
       <c r="V171" s="6">
-        <v>0.062900822153001898</v>
+        <v>0.035974975689816516</v>
       </c>
       <c r="W171" s="6">
-        <v>-0.010880339531739841</v>
+        <v>-0.0093031626850007369</v>
       </c>
       <c r="X171" s="8">
-        <v>37.967857142857142</v>
+        <v>38.359795614035086</v>
       </c>
       <c r="Y171" s="6">
-        <v>0.75</v>
+        <v>0.77192982456140347</v>
       </c>
       <c r="Z171" s="6">
-        <v>0.17857142857142858</v>
+        <v>0.2807017543859649</v>
       </c>
       <c r="AA171" s="8">
-        <v>8.3061403508771932</v>
+        <v>11.62681511111111</v>
       </c>
       <c r="AB171" s="8">
-        <v>17.529629629629628</v>
+        <v>12.72157767857143</v>
       </c>
       <c r="AC171" s="8">
-        <v>26.065261</v>
+        <v>24.041043999999999</v>
       </c>
       <c r="AD171" s="8">
-        <v>32.322617857142859</v>
+        <v>30.771199122807019</v>
       </c>
       <c r="AE171" s="6">
-        <v>0.32142857142857145</v>
+        <v>0.44736842105263158</v>
       </c>
       <c r="AF171" s="9"/>
       <c r="AG171" s="5">
-        <v>-297.02999999999997</v>
+        <v>-11058.389999999999</v>
       </c>
       <c r="AH171" s="10">
         <v>4</v>
@@ -23236,7 +23228,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR171" s="4">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c t="s" r="AS171" s="4">
         <v>56</v>
@@ -23256,7 +23248,7 @@
         <v>80</v>
       </c>
       <c t="s" r="E172" s="4">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c t="s" r="F172" s="4">
         <v>47</v>
@@ -23361,7 +23353,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR172" s="4">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c t="s" r="AS172" s="4">
         <v>56</v>
@@ -23381,7 +23373,7 @@
         <v>45</v>
       </c>
       <c t="s" r="E173" s="4">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c t="s" r="F173" s="4">
         <v>47</v>
@@ -23454,7 +23446,7 @@
         <v>55</v>
       </c>
       <c t="s" r="AR173" s="4">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c t="s" r="AS173" s="4">
         <v>56</v>
@@ -23474,7 +23466,7 @@
         <v>89</v>
       </c>
       <c t="s" r="E174" s="4">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c t="s" r="F174" s="4">
         <v>47</v>
@@ -23601,7 +23593,7 @@
         <v>80</v>
       </c>
       <c t="s" r="E175" s="4">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c t="s" r="F175" s="4">
         <v>47</v>
@@ -23682,10 +23674,10 @@
     </row>
     <row r="176" ht="24.75" customHeight="1">
       <c t="s" r="A176" s="14">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c t="s" r="B176" s="14">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="C176" s="15"/>
       <c r="D176" s="15"/>
@@ -23702,65 +23694,65 @@
         <v>52</v>
       </c>
       <c t="s" r="O176" s="14">
+        <v>283</v>
+      </c>
+      <c t="s" r="P176" s="14">
+        <v>284</v>
+      </c>
+      <c t="s" r="Q176" s="14">
         <v>285</v>
       </c>
-      <c t="s" r="P176" s="14">
+      <c t="s" r="R176" s="14">
         <v>286</v>
       </c>
-      <c t="s" r="Q176" s="14">
+      <c t="s" r="S176" s="14">
         <v>287</v>
       </c>
-      <c t="s" r="R176" s="14">
+      <c t="s" r="T176" s="14">
         <v>288</v>
       </c>
-      <c t="s" r="S176" s="14">
+      <c t="s" r="U176" s="14">
         <v>289</v>
       </c>
-      <c t="s" r="T176" s="14">
+      <c t="s" r="V176" s="14">
         <v>290</v>
       </c>
-      <c t="s" r="U176" s="14">
+      <c t="s" r="W176" s="14">
         <v>291</v>
       </c>
-      <c t="s" r="V176" s="14">
+      <c t="s" r="X176" s="14">
         <v>292</v>
       </c>
-      <c t="s" r="W176" s="14">
+      <c t="s" r="Y176" s="14">
         <v>293</v>
       </c>
-      <c t="s" r="X176" s="14">
+      <c t="s" r="Z176" s="14">
         <v>294</v>
       </c>
-      <c t="s" r="Y176" s="14">
+      <c t="s" r="AA176" s="14">
         <v>295</v>
       </c>
-      <c t="s" r="Z176" s="14">
+      <c t="s" r="AB176" s="14">
         <v>296</v>
       </c>
-      <c t="s" r="AA176" s="14">
+      <c t="s" r="AC176" s="14">
         <v>297</v>
       </c>
-      <c t="s" r="AB176" s="14">
+      <c t="s" r="AD176" s="14">
         <v>298</v>
       </c>
-      <c t="s" r="AC176" s="14">
+      <c t="s" r="AE176" s="14">
         <v>299</v>
-      </c>
-      <c t="s" r="AD176" s="14">
-        <v>300</v>
-      </c>
-      <c t="s" r="AE176" s="14">
-        <v>301</v>
       </c>
       <c r="AF176" s="14"/>
       <c t="s" r="AG176" s="14">
+        <v>300</v>
+      </c>
+      <c t="s" r="AH176" s="14">
+        <v>301</v>
+      </c>
+      <c t="s" r="AI176" s="14">
         <v>302</v>
-      </c>
-      <c t="s" r="AH176" s="14">
-        <v>303</v>
-      </c>
-      <c t="s" r="AI176" s="14">
-        <v>304</v>
       </c>
       <c r="AJ176" s="15"/>
       <c t="s" r="AK176" s="15">
@@ -23770,10 +23762,10 @@
         <v>52</v>
       </c>
       <c t="s" r="AM176" s="14">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c t="s" r="AN176" s="14">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="AO176" s="15"/>
       <c r="AP176" s="15"/>
